--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -6,26 +6,24 @@
     <sheet name="HDFC Bank" sheetId="1" r:id="rId1"/>
     <sheet name="ICICI Bank" sheetId="2" r:id="rId2"/>
     <sheet name="Axis Bank" sheetId="3" r:id="rId3"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="PNB" sheetId="5" r:id="rId5"/>
-    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
-    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="Indian Overseas Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="South Indian Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Federal Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Canara Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of Baroda" sheetId="13" r:id="rId13"/>
-    <sheet name="Bank of India" sheetId="14" r:id="rId14"/>
-    <sheet name="Bank of Maharashtra" sheetId="15" r:id="rId15"/>
-    <sheet name="RBL Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
-    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
-    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
-    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
-    <sheet name="Shriram Finance" sheetId="23" r:id="rId23"/>
+    <sheet name="PNB" sheetId="4" r:id="rId4"/>
+    <sheet name="IndusInd Bank" sheetId="5" r:id="rId5"/>
+    <sheet name="Yes Bank" sheetId="6" r:id="rId6"/>
+    <sheet name="IDFC First Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="Indian Overseas Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="Federal Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
+    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Indian Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Central Bank of India" sheetId="16" r:id="rId16"/>
+    <sheet name="Bandhan Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="PNB Housing Finance" sheetId="18" r:id="rId18"/>
+    <sheet name="KTDFC" sheetId="19" r:id="rId19"/>
+    <sheet name="LIC Housing Finance" sheetId="20" r:id="rId20"/>
+    <sheet name="Shriram Finance" sheetId="21" r:id="rId21"/>
   </sheets>
 </workbook>
 </file>
@@ -655,7 +653,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -675,21 +673,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 Days to 45 Days*</v>
       </c>
       <c r="B2">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 90 days</v>
+        <v>46 Days to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -697,29 +695,29 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 days to 99 days</v>
+        <v>91 Days to 179 Days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
+        <v>180 Days to 269 Days</v>
       </c>
       <c r="B5">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="C5">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 270 days</v>
+        <v>270 Days to less than 1 Year</v>
       </c>
       <c r="B6">
         <v>5.5</v>
@@ -730,168 +728,91 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
       </c>
       <c r="B7">
-        <v>5.9</v>
+        <v>6.25</v>
       </c>
       <c r="C7">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>444 Days*</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
+        <v>555 Days*</v>
       </c>
       <c r="B9">
-        <v>5.85</v>
+        <v>6.6</v>
       </c>
       <c r="C9">
-        <v>6.35</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>372 days</v>
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
+        <v>2 Years &amp; above to less than 3 Years</v>
       </c>
       <c r="B11">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="C11">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 months</v>
+        <v>3 Years &amp; above to less than 5 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
+        <v>5 Years &amp; above to 10 Years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -911,24 +832,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 29 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>30 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -936,10 +857,10 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
@@ -947,37 +868,37 @@
         <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
         <v>6</v>
-      </c>
-      <c r="C6">
-        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>182 days to 270 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -999,67 +920,281 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to less than 15 Months</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>15 Months</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 15 months to less than 36 months</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>36 months</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>7.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 36 months to 10 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.9</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1081,134 +1216,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>444 Days*</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>555 Days*</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1353,166 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1240,523 +1534,172 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 to 29 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30 to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 to 120 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>121 to 180 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>3.85</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>181 days to less than 9 months</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>9 months to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>444 days (Ind Secure Product)</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>555 days (Ind Green Product)</v>
       </c>
       <c r="B13">
         <v>6.4</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>5 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 30 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 179 days</v>
-      </c>
-      <c r="B6">
-        <v>4.25</v>
-      </c>
-      <c r="C6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>180 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.3</v>
-      </c>
-      <c r="C11">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>450 days</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.6</v>
-      </c>
-      <c r="C2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 119 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>120 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to 364 days</v>
-      </c>
-      <c r="B8">
-        <v>5.25</v>
-      </c>
-      <c r="C8">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
-      </c>
-      <c r="B10">
-        <v>6.15</v>
-      </c>
-      <c r="C10">
-        <v>6.15</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
-      </c>
-      <c r="B11">
-        <v>5.25</v>
-      </c>
-      <c r="C11">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 5 years</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1783,7 +1726,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1794,123 +1737,123 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -1921,198 +1864,6 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2134,134 +1885,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -2271,9 +2022,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C8"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2293,139 +2044,166 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>7.45</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>7.85</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 months - 71 months</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>7.65</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>72 months - 84 months</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>120 months</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2558,192 +2336,6 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months - 23 months</v>
-      </c>
-      <c r="B2">
-        <v>7.45</v>
-      </c>
-      <c r="C2">
-        <v>7.45</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>24 months - 35 months</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>36 months - 47 months</v>
-      </c>
-      <c r="B4">
-        <v>7.85</v>
-      </c>
-      <c r="C4">
-        <v>7.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>48 months - 59 months</v>
-      </c>
-      <c r="B5">
-        <v>7.4</v>
-      </c>
-      <c r="C5">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 months - 71 months</v>
-      </c>
-      <c r="B6">
-        <v>7.65</v>
-      </c>
-      <c r="C6">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>72 months - 84 months</v>
-      </c>
-      <c r="B7">
-        <v>7.4</v>
-      </c>
-      <c r="C7">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>120 months</v>
-      </c>
-      <c r="B8">
-        <v>7.4</v>
-      </c>
-      <c r="C8">
-        <v>7.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2835,7 +2427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3144,231 +2736,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3632,6 +2999,187 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to 364 days</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 Year to below 1 Year 6 Month</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 Year 6 months to below 1 Year 7 months</v>
+      </c>
+      <c r="B11">
+        <v>6.9</v>
+      </c>
+      <c r="C11">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 Year 7 months to below 2 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.9</v>
+      </c>
+      <c r="C12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 Years to 3 Years</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 3 Years up to below 61 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.65</v>
+      </c>
+      <c r="C14">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>61 Months and above</v>
+      </c>
+      <c r="B15">
+        <v>6.5</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3658,7 +3206,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -3669,7 +3217,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3680,7 +3228,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 60 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -3691,7 +3239,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>61 days to 90 days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -3702,51 +3250,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 180 days</v>
+        <v>121 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 210 days</v>
+        <v>181 days to 271 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>272 days to less than 12 months</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to 364 days</v>
+        <v>12 months</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
+        <v>12 months 1 day to less than 18 months</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -3757,57 +3305,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
+        <v>18 months</v>
       </c>
       <c r="B11">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="C11">
-        <v>7.4</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
+        <v>18 months 1 day to less than 24 months</v>
       </c>
       <c r="B12">
-        <v>6.9</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
+        <v>24 months to less than 36 months</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
+        <v>36 months to less than 60 months</v>
       </c>
       <c r="B14">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>7.15</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>61 Months and above</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B15">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -3818,6 +3366,176 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C14"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days – 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days – 29 days</v>
+      </c>
+      <c r="B3">
+        <v>3.25</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 days – 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.5</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days – 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days – 180 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days – less than 1 Year</v>
+      </c>
+      <c r="B7">
+        <v>6.5</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day – 370 days</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>371 days – 390 days</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>391 days – 499 days</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>500 days – 3 years</v>
+      </c>
+      <c r="B12">
+        <v>7.35</v>
+      </c>
+      <c r="C12">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3 years 1 day – 5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.75</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>5 years 1 day – 10 years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -3839,18 +3557,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7-14 Days*</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-29 Days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3861,134 +3579,135 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30-45 Days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>46-60 Days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>61-90 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>91-120 Days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>121-179 Days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>2.9</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>180-269 Days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>270 Days to &lt; 1 Year</v>
       </c>
       <c r="B10">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>444 Days</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>2 Years to &lt; 3 Years</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>3 Years and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3998,7 +3717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -4020,10 +3739,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days – 14 days</v>
+        <v>7 days to 29 days</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>3.5</v>
@@ -4031,76 +3750,76 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days – 29 days</v>
+        <v>30 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.25</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 days – 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days – 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
         <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days – 180 days</v>
+        <v>181 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days – less than 1 Year</v>
+        <v>182 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>271 days to less than 1 year</v>
       </c>
       <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
         <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day – 370 days</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
         <v>6.75</v>
@@ -4108,57 +3827,57 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>371 days – 390 days</v>
+        <v>Above 1 year to less than 15 Months</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>391 days – 499 days</v>
+        <v>15 Months</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.8</v>
       </c>
       <c r="C11">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>500 days – 3 years</v>
+        <v>Above 15 months to less than 36 months</v>
       </c>
       <c r="B12">
-        <v>7.35</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>3 years 1 day – 5 years</v>
+        <v>36 months</v>
       </c>
       <c r="B13">
         <v>6.75</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5 years 1 day – 10 years</v>
+        <v>Above 36 months to 10 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>6.25</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -4166,186 +3885,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7-14 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-29 Days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30-45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46-60 Days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61-90 Days</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91-120 Days</v>
-      </c>
-      <c r="B7">
-        <v>3.5</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>121-179 Days</v>
-      </c>
-      <c r="B8">
-        <v>2.9</v>
-      </c>
-      <c r="C8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>180-269 Days</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>444 Days</v>
-      </c>
-      <c r="B13">
-        <v>6.6</v>
-      </c>
-      <c r="C13">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
-      </c>
-      <c r="B14">
-        <v>6.4</v>
-      </c>
-      <c r="C14">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 Years and above</v>
-      </c>
-      <c r="B15">
-        <v>6.1</v>
-      </c>
-      <c r="C15">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -4,26 +4,28 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="HDFC Bank" sheetId="1" r:id="rId1"/>
-    <sheet name="ICICI Bank" sheetId="2" r:id="rId2"/>
-    <sheet name="Axis Bank" sheetId="3" r:id="rId3"/>
-    <sheet name="PNB" sheetId="4" r:id="rId4"/>
-    <sheet name="IndusInd Bank" sheetId="5" r:id="rId5"/>
-    <sheet name="Yes Bank" sheetId="6" r:id="rId6"/>
-    <sheet name="IDFC First Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="Indian Overseas Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="Federal Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
-    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Indian Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Central Bank of India" sheetId="16" r:id="rId16"/>
-    <sheet name="Bandhan Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="PNB Housing Finance" sheetId="18" r:id="rId18"/>
-    <sheet name="KTDFC" sheetId="19" r:id="rId19"/>
-    <sheet name="LIC Housing Finance" sheetId="20" r:id="rId20"/>
-    <sheet name="Shriram Finance" sheetId="21" r:id="rId21"/>
+    <sheet name="SBI" sheetId="2" r:id="rId2"/>
+    <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
+    <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
+    <sheet name="PNB" sheetId="6" r:id="rId6"/>
+    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Indian Overseas Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="South Indian Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Federal Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of Baroda" sheetId="13" r:id="rId13"/>
+    <sheet name="Bank of India" sheetId="14" r:id="rId14"/>
+    <sheet name="Bank of Maharashtra" sheetId="15" r:id="rId15"/>
+    <sheet name="RBL Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
+    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
+    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
+    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
+    <sheet name="Shriram Finance" sheetId="23" r:id="rId23"/>
   </sheets>
 </workbook>
 </file>
@@ -653,7 +655,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -673,21 +675,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
+        <v>7-14 Days*</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
+        <v>15-29 Days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -695,122 +697,551 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
+        <v>30-45 Days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
+        <v>46-60 Days</v>
       </c>
       <c r="B5">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
+        <v>61-90 Days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+        <v>91-120 Days</v>
       </c>
       <c r="B7">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>444 Days*</v>
+        <v>121-179 Days</v>
       </c>
       <c r="B8">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>555 Days*</v>
+        <v>180-269 Days</v>
       </c>
       <c r="B9">
-        <v>6.6</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+        <v>270 Days to &lt; 1 Year</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
+        <v>1 Year</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
+        <v>444 Days</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 Years to &lt; 3 Years</v>
+      </c>
+      <c r="B14">
+        <v>6.4</v>
+      </c>
+      <c r="C14">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 Years and above</v>
+      </c>
+      <c r="B15">
+        <v>6.1</v>
+      </c>
+      <c r="C15">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C14"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 29 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>30 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.25</v>
+      </c>
+      <c r="C3">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>182 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to less than 15 Months</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>15 Months</v>
+      </c>
+      <c r="B11">
+        <v>6.8</v>
+      </c>
+      <c r="C11">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 15 months to less than 36 months</v>
+      </c>
+      <c r="B12">
+        <v>6.4</v>
+      </c>
+      <c r="C12">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>36 months</v>
+      </c>
+      <c r="B13">
+        <v>6.75</v>
+      </c>
+      <c r="C13">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 36 months to 10 years</v>
+      </c>
+      <c r="B14">
+        <v>6.4</v>
+      </c>
+      <c r="C14">
+        <v>6.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1002,7 +1433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1194,7 +1625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1349,357 +1780,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 240 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>241 days to 364 days</v>
-      </c>
-      <c r="B7">
-        <v>6.05</v>
-      </c>
-      <c r="C7">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>18 months to 24 months</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
-      </c>
-      <c r="B11">
-        <v>7.2</v>
-      </c>
-      <c r="C11">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B13">
-        <v>6.7</v>
-      </c>
-      <c r="C13">
-        <v>7.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1726,7 +1806,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1737,123 +1817,123 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1864,6 +1944,198 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1885,134 +2157,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -2022,7 +2294,303 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C11"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 45 days</v>
+      </c>
+      <c r="B2">
+        <v>3.05</v>
+      </c>
+      <c r="C2">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 days to 179 days</v>
+      </c>
+      <c r="B3">
+        <v>4.9</v>
+      </c>
+      <c r="C3">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B4">
+        <v>5.65</v>
+      </c>
+      <c r="C4">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>211 days to less than 1 year</v>
+      </c>
+      <c r="B5">
+        <v>5.9</v>
+      </c>
+      <c r="C5">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1 Year to less than 2 years</v>
+      </c>
+      <c r="B6">
+        <v>6.25</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B7">
+        <v>6.45</v>
+      </c>
+      <c r="C7">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B8">
+        <v>6.3</v>
+      </c>
+      <c r="C8">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>5 years and up to 10 years</v>
+      </c>
+      <c r="B9">
+        <v>6.05</v>
+      </c>
+      <c r="C9">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B10">
+        <v>6.55</v>
+      </c>
+      <c r="C10">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.8</v>
+      </c>
+      <c r="C11">
+        <v>7.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -2122,307 +2690,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 45 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 to 184 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
-      </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
-      </c>
-      <c r="B6">
-        <v>6.25</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
-      </c>
-      <c r="B7">
-        <v>6.3</v>
-      </c>
-      <c r="C7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
-      </c>
-      <c r="B8">
-        <v>6.45</v>
-      </c>
-      <c r="C8">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B4">
-        <v>6.75</v>
-      </c>
-      <c r="C4">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
-      </c>
-      <c r="C5">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B6">
-        <v>6.85</v>
-      </c>
-      <c r="C6">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B7">
-        <v>6.9</v>
-      </c>
-      <c r="C7">
-        <v>6.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2449,6 +2716,181 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B4">
+        <v>6.75</v>
+      </c>
+      <c r="C4">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B5">
+        <v>6.8</v>
+      </c>
+      <c r="C5">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B6">
+        <v>6.85</v>
+      </c>
+      <c r="C6">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B7">
+        <v>6.9</v>
+      </c>
+      <c r="C7">
+        <v>6.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
         <v>12 Months</v>
       </c>
       <c r="B2">
@@ -2510,6 +2952,132 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 45 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 to 184 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>185 to &lt; 1 Year</v>
+      </c>
+      <c r="B5">
+        <v>5.5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1 Year to &lt; 18 Months</v>
+      </c>
+      <c r="B6">
+        <v>6.25</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>18 Months to 2 Years</v>
+      </c>
+      <c r="B7">
+        <v>6.3</v>
+      </c>
+      <c r="C7">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2 Years 1 Day to 3 Years</v>
+      </c>
+      <c r="B8">
+        <v>6.45</v>
+      </c>
+      <c r="C8">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>3 Years 1 Day to 5 Years</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>5 Years 1 Day to 10 Years</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C19"/>
   <cols>
@@ -2734,7 +3302,232 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -3003,7 +3796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -3180,357 +3973,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 120 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>121 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 271 days</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>12 months</v>
-      </c>
-      <c r="B9">
-        <v>6.65</v>
-      </c>
-      <c r="C9">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
-      </c>
-      <c r="B10">
-        <v>6.75</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.75</v>
-      </c>
-      <c r="C11">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
-      </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
-      </c>
-      <c r="B14">
-        <v>7</v>
-      </c>
-      <c r="C14">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B15">
-        <v>6.75</v>
-      </c>
-      <c r="C15">
-        <v>7.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days – 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days – 29 days</v>
-      </c>
-      <c r="B3">
-        <v>3.25</v>
-      </c>
-      <c r="C3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 days – 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days – 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days – 180 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days – less than 1 Year</v>
-      </c>
-      <c r="B7">
-        <v>6.5</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day – 370 days</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>371 days – 390 days</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>391 days – 499 days</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>500 days – 3 years</v>
-      </c>
-      <c r="B12">
-        <v>7.35</v>
-      </c>
-      <c r="C12">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>3 years 1 day – 5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.75</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>5 years 1 day – 10 years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>6.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3557,18 +3999,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7-14 Days*</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-29 Days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3579,135 +4021,134 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30-45 Days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46-60 Days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61-90 Days</v>
+        <v>121 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91-120 Days</v>
+        <v>181 days to 271 days</v>
       </c>
       <c r="B7">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>121-179 Days</v>
+        <v>272 days to less than 12 months</v>
       </c>
       <c r="B8">
-        <v>2.9</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>3.4</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>180-269 Days</v>
+        <v>12 months</v>
       </c>
       <c r="B9">
-        <v>4.75</v>
+        <v>6.65</v>
       </c>
       <c r="C9">
-        <v>5.25</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
+        <v>12 months 1 day to less than 18 months</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year</v>
+        <v>18 months</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months 1 day to less than 24 months</v>
       </c>
       <c r="B12">
-        <v>6.4</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>444 Days</v>
+        <v>24 months to less than 36 months</v>
       </c>
       <c r="B13">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
+        <v>36 months to less than 60 months</v>
       </c>
       <c r="B14">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>6.9</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3 Years and above</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B15">
-        <v>6.1</v>
+        <v>6.75</v>
       </c>
       <c r="C15">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -3739,10 +4180,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 29 days</v>
+        <v>7 days – 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C2">
         <v>3.5</v>
@@ -3750,76 +4191,76 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>30 days to 45 days</v>
+        <v>15 days – 29 days</v>
       </c>
       <c r="B3">
         <v>3.25</v>
       </c>
       <c r="C3">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30 days – 45 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days – 90 days</v>
       </c>
       <c r="B5">
         <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days</v>
+        <v>91 days – 180 days</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>182 days to 270 days</v>
+        <v>181 days – less than 1 Year</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>1 year 1 day – 370 days</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
         <v>6.75</v>
@@ -3827,57 +4268,57 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to less than 15 Months</v>
+        <v>371 days – 390 days</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>15 Months</v>
+        <v>391 days – 499 days</v>
       </c>
       <c r="B11">
-        <v>6.8</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 15 months to less than 36 months</v>
+        <v>500 days – 3 years</v>
       </c>
       <c r="B12">
-        <v>6.4</v>
+        <v>7.35</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>36 months</v>
+        <v>3 years 1 day – 5 years</v>
       </c>
       <c r="B13">
         <v>6.75</v>
       </c>
       <c r="C13">
-        <v>7.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 36 months to 10 years</v>
+        <v>5 years 1 day – 10 years</v>
       </c>
       <c r="B14">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.9</v>
+        <v>6.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -13,19 +13,18 @@
     <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
     <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
     <sheet name="Indian Overseas Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="South Indian Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Federal Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of Baroda" sheetId="13" r:id="rId13"/>
-    <sheet name="Bank of India" sheetId="14" r:id="rId14"/>
-    <sheet name="Bank of Maharashtra" sheetId="15" r:id="rId15"/>
-    <sheet name="RBL Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
-    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
-    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
-    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
-    <sheet name="Shriram Finance" sheetId="23" r:id="rId23"/>
+    <sheet name="Federal Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
+    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
+    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
+    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
+    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
+    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
+    <sheet name="Shriram Finance" sheetId="22" r:id="rId22"/>
   </sheets>
 </workbook>
 </file>
@@ -837,242 +836,6 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.9</v>
-      </c>
-      <c r="C2">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 90 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 days to 99 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.8</v>
-      </c>
-      <c r="C5">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>5.9</v>
-      </c>
-      <c r="C7">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
-      </c>
-      <c r="B9">
-        <v>5.85</v>
-      </c>
-      <c r="C9">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>372 days</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.05</v>
-      </c>
-      <c r="C11">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -1237,6 +1000,198 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1266,150 +1221,150 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1417,13 +1372,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1435,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1455,172 +1410,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1647,24 +1569,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -1672,109 +1594,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.25</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1785,6 +1707,198 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1806,7 +1920,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1817,320 +1931,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2157,134 +2079,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -2296,7 +2218,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C8"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2316,139 +2238,84 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>7.45</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>7.85</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 months - 71 months</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>7.65</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>72 months - 84 months</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>120 months</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2592,110 +2459,6 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months - 23 months</v>
-      </c>
-      <c r="B2">
-        <v>7.45</v>
-      </c>
-      <c r="C2">
-        <v>7.45</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>24 months - 35 months</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>36 months - 47 months</v>
-      </c>
-      <c r="B4">
-        <v>7.85</v>
-      </c>
-      <c r="C4">
-        <v>7.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>48 months - 59 months</v>
-      </c>
-      <c r="B5">
-        <v>7.4</v>
-      </c>
-      <c r="C5">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 months - 71 months</v>
-      </c>
-      <c r="B6">
-        <v>7.65</v>
-      </c>
-      <c r="C6">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>72 months - 84 months</v>
-      </c>
-      <c r="B7">
-        <v>7.4</v>
-      </c>
-      <c r="C7">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>120 months</v>
-      </c>
-      <c r="B8">
-        <v>7.4</v>
-      </c>
-      <c r="C8">
-        <v>7.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2776,7 +2539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
@@ -2869,7 +2632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -13,18 +13,19 @@
     <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
     <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
     <sheet name="Indian Overseas Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Federal Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
-    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
-    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
-    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
-    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
-    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
-    <sheet name="Shriram Finance" sheetId="22" r:id="rId22"/>
+    <sheet name="South Indian Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Federal Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of Baroda" sheetId="13" r:id="rId13"/>
+    <sheet name="Bank of India" sheetId="14" r:id="rId14"/>
+    <sheet name="Bank of Maharashtra" sheetId="15" r:id="rId15"/>
+    <sheet name="RBL Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
+    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
+    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
+    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
+    <sheet name="Shriram Finance" sheetId="23" r:id="rId23"/>
   </sheets>
 </workbook>
 </file>
@@ -836,6 +837,242 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -1000,198 +1237,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1221,150 +1266,150 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>Above 10 years (MACAD only)</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1372,13 +1417,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1390,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1410,139 +1455,172 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1569,24 +1647,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -1594,109 +1672,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1707,6 +1785,165 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1894,165 +2131,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2079,134 +2157,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -2218,7 +2296,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2238,84 +2316,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>7.45</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>7.45</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>7.85</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>7.85</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>7.4</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months - 71 months</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>7.65</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>7.65</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>72 months - 84 months</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>7.4</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>120 months</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>7.4</v>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2459,6 +2592,110 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months - 23 months</v>
+      </c>
+      <c r="B2">
+        <v>7.45</v>
+      </c>
+      <c r="C2">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>24 months - 35 months</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>36 months - 47 months</v>
+      </c>
+      <c r="B4">
+        <v>7.85</v>
+      </c>
+      <c r="C4">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>48 months - 59 months</v>
+      </c>
+      <c r="B5">
+        <v>7.4</v>
+      </c>
+      <c r="C5">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>60 months - 71 months</v>
+      </c>
+      <c r="B6">
+        <v>7.65</v>
+      </c>
+      <c r="C6">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>72 months - 84 months</v>
+      </c>
+      <c r="B7">
+        <v>7.4</v>
+      </c>
+      <c r="C7">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>120 months</v>
+      </c>
+      <c r="B8">
+        <v>7.4</v>
+      </c>
+      <c r="C8">
+        <v>7.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2539,7 +2776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
@@ -2632,7 +2869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -3256,10 +3256,10 @@
         <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>6.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3267,10 +3267,10 @@
         <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -3278,10 +3278,10 @@
         <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>6.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -3289,10 +3289,10 @@
         <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -12,20 +12,19 @@
     <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
     <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
     <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Indian Overseas Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="South Indian Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Federal Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of Baroda" sheetId="13" r:id="rId13"/>
-    <sheet name="Bank of India" sheetId="14" r:id="rId14"/>
-    <sheet name="Bank of Maharashtra" sheetId="15" r:id="rId15"/>
-    <sheet name="RBL Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
-    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
-    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
-    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
-    <sheet name="Shriram Finance" sheetId="23" r:id="rId23"/>
+    <sheet name="South Indian Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Federal Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
+    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
+    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
+    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
+    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
+    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
+    <sheet name="Shriram Finance" sheetId="22" r:id="rId22"/>
   </sheets>
 </workbook>
 </file>
@@ -655,188 +654,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7-14 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-29 Days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30-45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46-60 Days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61-90 Days</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91-120 Days</v>
-      </c>
-      <c r="B7">
-        <v>3.5</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>121-179 Days</v>
-      </c>
-      <c r="B8">
-        <v>2.9</v>
-      </c>
-      <c r="C8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>180-269 Days</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>444 Days</v>
-      </c>
-      <c r="B13">
-        <v>6.6</v>
-      </c>
-      <c r="C13">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
-      </c>
-      <c r="B14">
-        <v>6.4</v>
-      </c>
-      <c r="C14">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 Years and above</v>
-      </c>
-      <c r="B15">
-        <v>6.1</v>
-      </c>
-      <c r="C15">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -1071,7 +888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -1237,6 +1054,198 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1266,150 +1275,150 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1417,13 +1426,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1435,7 +1444,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1455,172 +1464,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1647,24 +1623,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -1672,109 +1648,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.25</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1785,6 +1761,198 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1806,7 +1974,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1817,320 +1985,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2157,134 +2133,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -2296,7 +2272,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C8"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2316,139 +2292,84 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>7.45</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>7.85</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 months - 71 months</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>7.65</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>72 months - 84 months</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>120 months</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2592,110 +2513,6 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months - 23 months</v>
-      </c>
-      <c r="B2">
-        <v>7.45</v>
-      </c>
-      <c r="C2">
-        <v>7.45</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>24 months - 35 months</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>36 months - 47 months</v>
-      </c>
-      <c r="B4">
-        <v>7.85</v>
-      </c>
-      <c r="C4">
-        <v>7.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>48 months - 59 months</v>
-      </c>
-      <c r="B5">
-        <v>7.4</v>
-      </c>
-      <c r="C5">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 months - 71 months</v>
-      </c>
-      <c r="B6">
-        <v>7.65</v>
-      </c>
-      <c r="C6">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>72 months - 84 months</v>
-      </c>
-      <c r="B7">
-        <v>7.4</v>
-      </c>
-      <c r="C7">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>120 months</v>
-      </c>
-      <c r="B8">
-        <v>7.4</v>
-      </c>
-      <c r="C8">
-        <v>7.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2776,7 +2593,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
@@ -2869,7 +2686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -5,13 +5,13 @@
   <sheets>
     <sheet name="HDFC Bank" sheetId="1" r:id="rId1"/>
     <sheet name="SBI" sheetId="2" r:id="rId2"/>
-    <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
-    <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
-    <sheet name="PNB" sheetId="6" r:id="rId6"/>
-    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Axis Bank" sheetId="3" r:id="rId3"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="4" r:id="rId4"/>
+    <sheet name="PNB" sheetId="5" r:id="rId5"/>
+    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
+    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="Indian Overseas Bank" sheetId="9" r:id="rId9"/>
     <sheet name="South Indian Bank" sheetId="10" r:id="rId10"/>
     <sheet name="Federal Bank" sheetId="11" r:id="rId11"/>
     <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
@@ -2770,7 +2770,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2790,106 +2790,205 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 to 45 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 to 90 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 to 184 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
         <v>6.5</v>
       </c>
-      <c r="C10">
+      <c r="C16">
         <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2916,73 +3015,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 - 14 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>15 - 30 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>31 - 45 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>46 - 90 Days</v>
       </c>
       <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>91 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>92 Days - 179 Days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>180 Days</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -2993,18 +3092,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>181 Days to 269 Days</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>270 Days</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -3015,101 +3114,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>271 Days to 363 Days</v>
       </c>
       <c r="B11">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>364 Days</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>365 Days to less than 15 Months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>15 Months - less than 18 Months</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>18 months - less than 2 years</v>
       </c>
       <c r="B15">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="C15">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>2 years- less than 3 years</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>3 years and above but less than 4 years</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>4 years and above but less than 5 years</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years to 10 years</v>
+        <v>5 years and above upto and inclusive of 10 years</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3120,231 +3219,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -3609,6 +3483,187 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to 364 days</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 Year to below 1 Year 6 Month</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 Year 6 months to below 1 Year 7 months</v>
+      </c>
+      <c r="B11">
+        <v>6.9</v>
+      </c>
+      <c r="C11">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 Year 7 months to below 2 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.9</v>
+      </c>
+      <c r="C12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 Years to 3 Years</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 3 Years up to below 61 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.65</v>
+      </c>
+      <c r="C14">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>61 Months and above</v>
+      </c>
+      <c r="B15">
+        <v>6.5</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3635,7 +3690,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -3646,7 +3701,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3657,7 +3712,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 60 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -3668,7 +3723,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>61 days to 90 days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -3679,51 +3734,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 180 days</v>
+        <v>121 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 210 days</v>
+        <v>181 days to 271 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>272 days to less than 12 months</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to 364 days</v>
+        <v>12 months</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
+        <v>12 months 1 day to less than 18 months</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -3734,57 +3789,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
+        <v>18 months</v>
       </c>
       <c r="B11">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="C11">
-        <v>7.4</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
+        <v>18 months 1 day to less than 24 months</v>
       </c>
       <c r="B12">
-        <v>6.9</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
+        <v>24 months to less than 36 months</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
+        <v>36 months to less than 60 months</v>
       </c>
       <c r="B14">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>7.15</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>61 Months and above</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B15">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -3795,6 +3850,176 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C14"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days – 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days – 29 days</v>
+      </c>
+      <c r="B3">
+        <v>3.25</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 days – 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.5</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days – 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days – 180 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days – less than 1 Year</v>
+      </c>
+      <c r="B7">
+        <v>6.5</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day – 370 days</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>371 days – 390 days</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>391 days – 499 days</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>500 days – 3 years</v>
+      </c>
+      <c r="B12">
+        <v>7.35</v>
+      </c>
+      <c r="C12">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3 years 1 day – 5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.75</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>5 years 1 day – 10 years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -3816,18 +4041,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7-14 Days*</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-29 Days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3838,134 +4063,135 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30-45 Days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>46-60 Days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>61-90 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>91-120 Days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>121-179 Days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>2.9</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>180-269 Days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>270 Days to &lt; 1 Year</v>
       </c>
       <c r="B10">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>444 Days</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>2 Years to &lt; 3 Years</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>3 Years and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3973,174 +4199,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days – 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days – 29 days</v>
-      </c>
-      <c r="B3">
-        <v>3.25</v>
-      </c>
-      <c r="C3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 days – 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days – 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days – 180 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days – less than 1 Year</v>
-      </c>
-      <c r="B7">
-        <v>6.5</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day – 370 days</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>371 days – 390 days</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>391 days – 499 days</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>500 days – 3 years</v>
-      </c>
-      <c r="B12">
-        <v>7.35</v>
-      </c>
-      <c r="C12">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>3 years 1 day – 5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.75</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>5 years 1 day – 10 years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>6.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -5,14 +5,14 @@
   <sheets>
     <sheet name="HDFC Bank" sheetId="1" r:id="rId1"/>
     <sheet name="SBI" sheetId="2" r:id="rId2"/>
-    <sheet name="Axis Bank" sheetId="3" r:id="rId3"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="PNB" sheetId="5" r:id="rId5"/>
-    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
-    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="Indian Overseas Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="South Indian Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
+    <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
+    <sheet name="PNB" sheetId="6" r:id="rId6"/>
+    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Indian Overseas Bank" sheetId="10" r:id="rId10"/>
     <sheet name="Federal Bank" sheetId="11" r:id="rId11"/>
     <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
     <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
@@ -654,7 +654,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -674,18 +674,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7-14 Days*</v>
       </c>
       <c r="B2">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 90 days</v>
+        <v>15-29 Days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -696,194 +696,140 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 days to 99 days</v>
+        <v>30-45 Days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
+        <v>46-60 Days</v>
       </c>
       <c r="B5">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 270 days</v>
+        <v>61-90 Days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>91-120 Days</v>
       </c>
       <c r="B7">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>6.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>121-179 Days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>2.9</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
+        <v>180-269 Days</v>
       </c>
       <c r="B9">
-        <v>5.85</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>6.35</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>372 days</v>
+        <v>270 Days to &lt; 1 Year</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
+        <v>1 Year</v>
       </c>
       <c r="B11">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
+        <v>444 Days</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.6</v>
       </c>
       <c r="C13">
-        <v>6.35</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>30 months</v>
+        <v>2 Years to &lt; 3 Years</v>
       </c>
       <c r="B14">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
+        <v>3 Years and above</v>
       </c>
       <c r="B15">
-        <v>5.85</v>
+        <v>6.1</v>
       </c>
       <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2770,7 +2716,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2790,205 +2736,106 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 to 45 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>46 to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>91 to 184 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>185 to &lt; 1 Year</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>1 Year to &lt; 18 Months</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>18 Months to 2 Years</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
         <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3015,73 +2862,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 - 30 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 - 90 Days</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 Days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 Days</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -3092,18 +2939,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
         <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -3114,101 +2961,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>364 Days</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -3219,6 +3066,231 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -3483,187 +3555,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to 364 days</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
-      </c>
-      <c r="B10">
-        <v>6.75</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
-      </c>
-      <c r="B11">
-        <v>6.9</v>
-      </c>
-      <c r="C11">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.9</v>
-      </c>
-      <c r="C12">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
-      </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.65</v>
-      </c>
-      <c r="C14">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>61 Months and above</v>
-      </c>
-      <c r="B15">
-        <v>6.5</v>
-      </c>
-      <c r="C15">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3690,7 +3581,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -3701,7 +3592,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3712,7 +3603,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>46 days to 60 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -3723,7 +3614,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>61 days to 90 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -3734,51 +3625,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>270 days to 364 days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>1 Year to below 1 Year 6 Month</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -3789,57 +3680,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year 6 months to below 1 Year 7 months</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.9</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>1 Year 7 months to below 2 Years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>2 Years to 3 Years</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>Above 3 Years up to below 61 Months</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>61 Months and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3850,6 +3741,187 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 120 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>121 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 271 days</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>272 days to less than 12 months</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B9">
+        <v>6.65</v>
+      </c>
+      <c r="C9">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>12 months 1 day to less than 18 months</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.75</v>
+      </c>
+      <c r="C11">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months 1 day to less than 24 months</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>24 months to less than 36 months</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>36 months to less than 60 months</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>7.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -4017,186 +4089,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7-14 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-29 Days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30-45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46-60 Days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61-90 Days</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91-120 Days</v>
-      </c>
-      <c r="B7">
-        <v>3.5</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>121-179 Days</v>
-      </c>
-      <c r="B8">
-        <v>2.9</v>
-      </c>
-      <c r="C8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>180-269 Days</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>444 Days</v>
-      </c>
-      <c r="B13">
-        <v>6.6</v>
-      </c>
-      <c r="C13">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
-      </c>
-      <c r="B14">
-        <v>6.4</v>
-      </c>
-      <c r="C14">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 Years and above</v>
-      </c>
-      <c r="B15">
-        <v>6.1</v>
-      </c>
-      <c r="C15">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -4,27 +4,25 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="HDFC Bank" sheetId="1" r:id="rId1"/>
-    <sheet name="SBI" sheetId="2" r:id="rId2"/>
-    <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
-    <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
-    <sheet name="PNB" sheetId="6" r:id="rId6"/>
-    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Indian Overseas Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Federal Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
-    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
-    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
-    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
-    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
-    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
-    <sheet name="Shriram Finance" sheetId="22" r:id="rId22"/>
+    <sheet name="ICICI Bank" sheetId="2" r:id="rId2"/>
+    <sheet name="Axis Bank" sheetId="3" r:id="rId3"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="4" r:id="rId4"/>
+    <sheet name="PNB" sheetId="5" r:id="rId5"/>
+    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
+    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="Federal Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Bank of Baroda" sheetId="10" r:id="rId10"/>
+    <sheet name="Bank of India" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of Maharashtra" sheetId="12" r:id="rId12"/>
+    <sheet name="RBL Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="Indian Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Central Bank of India" sheetId="15" r:id="rId15"/>
+    <sheet name="Bandhan Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="PNB Housing Finance" sheetId="17" r:id="rId17"/>
+    <sheet name="KTDFC" sheetId="18" r:id="rId18"/>
+    <sheet name="LIC Housing Finance" sheetId="19" r:id="rId19"/>
+    <sheet name="Shriram Finance" sheetId="20" r:id="rId20"/>
   </sheets>
 </workbook>
 </file>
@@ -654,7 +652,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -674,7 +672,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7-14 Days*</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -685,7 +683,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-29 Days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -696,84 +694,84 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30-45 Days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46-60 Days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61-90 Days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>3.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91-120 Days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>121-179 Days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>180-269 Days</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
         <v>6.5</v>
@@ -782,229 +780,69 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>444 Days</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3 Years and above</v>
+        <v>Above 10 years (MACAD only)</v>
       </c>
       <c r="B15">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
         <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 29 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>30 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.25</v>
-      </c>
-      <c r="C3">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.25</v>
-      </c>
-      <c r="C4">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>182 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to less than 15 Months</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>15 Months</v>
-      </c>
-      <c r="B11">
-        <v>6.8</v>
-      </c>
-      <c r="C11">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 15 months to less than 36 months</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>36 months</v>
-      </c>
-      <c r="B13">
-        <v>6.75</v>
-      </c>
-      <c r="C13">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 36 months to 10 years</v>
-      </c>
-      <c r="B14">
-        <v>6.4</v>
-      </c>
-      <c r="C14">
-        <v>6.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1029,150 +867,150 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1180,13 +1018,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1196,7 +1034,325 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.6</v>
+      </c>
+      <c r="C2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>3.75</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 119 days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>120 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to 364 days</v>
+      </c>
+      <c r="B8">
+        <v>5.25</v>
+      </c>
+      <c r="C8">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 2 years</v>
+      </c>
+      <c r="B10">
+        <v>6.15</v>
+      </c>
+      <c r="C10">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 2 years to 3 years</v>
+      </c>
+      <c r="B11">
+        <v>5.25</v>
+      </c>
+      <c r="C11">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above3 years to 5 years</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 5 years</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1218,90 +1374,90 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 to 29 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>30 to 45 days</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>46 to 90 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>91 to 120 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>121 to 180 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>181 days to less than 9 months</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>9 months to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
@@ -1309,240 +1465,81 @@
         <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="C10">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="C11">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>444 days (Ind Secure Product)</v>
       </c>
       <c r="B12">
         <v>6.6</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>555 days (Ind Green Product)</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C14">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>5 years</v>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.6</v>
-      </c>
-      <c r="C2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 119 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>120 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to 364 days</v>
-      </c>
-      <c r="B8">
-        <v>5.25</v>
-      </c>
-      <c r="C8">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
-      </c>
-      <c r="B10">
-        <v>6.15</v>
-      </c>
-      <c r="C10">
-        <v>6.15</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
-      </c>
-      <c r="B11">
-        <v>5.25</v>
-      </c>
-      <c r="C11">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 5 years</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1569,7 +1566,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1580,123 +1577,123 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -1707,198 +1704,6 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1920,134 +1725,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -2057,166 +1862,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -2320,9 +1966,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2342,51 +1988,226 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 45 days</v>
+        <v>1 year</v>
       </c>
       <c r="B2">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>3.55</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 days to 179 days</v>
+        <v>2 years</v>
       </c>
       <c r="B3">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>5.4</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>180 days to 210 days</v>
+        <v>3 years</v>
       </c>
       <c r="B4">
-        <v>5.65</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>6.15</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>211 days to less than 1 year</v>
+        <v>4 years</v>
       </c>
       <c r="B5">
-        <v>5.9</v>
+        <v>6.75</v>
       </c>
       <c r="C5">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to less than 2 years</v>
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B4">
+        <v>6.75</v>
+      </c>
+      <c r="C4">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B5">
+        <v>6.8</v>
+      </c>
+      <c r="C5">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B6">
+        <v>6.85</v>
+      </c>
+      <c r="C6">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B7">
+        <v>6.9</v>
+      </c>
+      <c r="C7">
+        <v>6.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 45 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 to 184 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>185 to &lt; 1 Year</v>
+      </c>
+      <c r="B5">
+        <v>5.5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1 Year to &lt; 18 Months</v>
       </c>
       <c r="B6">
         <v>6.25</v>
@@ -2397,62 +2218,51 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>18 Months to 2 Years</v>
       </c>
       <c r="B7">
-        <v>6.45</v>
+        <v>6.3</v>
       </c>
       <c r="C7">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="C8">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>5 years and up to 10 years</v>
+        <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>7.05</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year</v>
+        <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.8</v>
-      </c>
-      <c r="C11">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2479,21 +2289,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>12 Months</v>
       </c>
       <c r="B2">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>7.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2 years</v>
+        <v>15 Months</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="C3">
         <v>7.25</v>
@@ -2501,35 +2311,35 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3 years</v>
+        <v>18-23</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
       <c r="C4">
-        <v>7.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4 years</v>
+        <v>24-35</v>
       </c>
       <c r="B5">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5 years</v>
+        <v>36-60</v>
       </c>
       <c r="B6">
-        <v>6.75</v>
+        <v>7.6</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -2539,9 +2349,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2561,281 +2371,205 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>6.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 months</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>6.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>18 months</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>6.75</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>6.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 years</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 years</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>6.85</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6.85</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>5 years</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.9</v>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>3 months 25 days &lt; 4 months</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>4 months &lt; 6 months</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>6 months &lt; 9 months</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
+        <v>6.5</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 Months</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 Months</v>
-      </c>
-      <c r="B3">
-        <v>7.25</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18-23</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>24-35</v>
-      </c>
-      <c r="B5">
-        <v>7.25</v>
-      </c>
-      <c r="C5">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>36-60</v>
-      </c>
-      <c r="B6">
-        <v>7.6</v>
-      </c>
-      <c r="C6">
-        <v>7.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 45 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 to 184 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
-      </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
-      </c>
-      <c r="B6">
-        <v>6.25</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
-      </c>
-      <c r="B7">
-        <v>6.3</v>
-      </c>
-      <c r="C7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
-      </c>
-      <c r="B8">
-        <v>6.45</v>
-      </c>
-      <c r="C8">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2862,73 +2596,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 - 14 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>15 - 30 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>31 - 45 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>46 - 90 Days</v>
       </c>
       <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>91 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>92 Days - 179 Days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>180 Days</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -2939,18 +2673,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>181 Days to 269 Days</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>270 Days</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -2961,101 +2695,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>271 Days to 363 Days</v>
       </c>
       <c r="B11">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>364 Days</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>365 Days to less than 15 Months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>15 Months - less than 18 Months</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>18 months - less than 2 years</v>
       </c>
       <c r="B15">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="C15">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>2 years- less than 3 years</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>3 years and above but less than 4 years</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>4 years and above but less than 5 years</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years to 10 years</v>
+        <v>5 years and above upto and inclusive of 10 years</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3066,231 +2800,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -3555,6 +3064,187 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to 364 days</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 Year to below 1 Year 6 Month</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 Year 6 months to below 1 Year 7 months</v>
+      </c>
+      <c r="B11">
+        <v>6.9</v>
+      </c>
+      <c r="C11">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 Year 7 months to below 2 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.9</v>
+      </c>
+      <c r="C12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 Years to 3 Years</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 3 Years up to below 61 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.65</v>
+      </c>
+      <c r="C14">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>61 Months and above</v>
+      </c>
+      <c r="B15">
+        <v>6.5</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3581,7 +3271,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -3592,7 +3282,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3603,7 +3293,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 60 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -3614,7 +3304,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>61 days to 90 days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -3625,51 +3315,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 180 days</v>
+        <v>121 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 210 days</v>
+        <v>181 days to 271 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>272 days to less than 12 months</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to 364 days</v>
+        <v>12 months</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
+        <v>12 months 1 day to less than 18 months</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -3680,57 +3370,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
+        <v>18 months</v>
       </c>
       <c r="B11">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="C11">
-        <v>7.4</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
+        <v>18 months 1 day to less than 24 months</v>
       </c>
       <c r="B12">
-        <v>6.9</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
+        <v>24 months to less than 36 months</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
+        <v>36 months to less than 60 months</v>
       </c>
       <c r="B14">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>7.15</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>61 Months and above</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B15">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -3742,7 +3432,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3762,54 +3452,54 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days – 14 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
       </c>
       <c r="C2">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days – 29 days</v>
       </c>
       <c r="B3">
+        <v>3.25</v>
+      </c>
+      <c r="C3">
         <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30 days – 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>46 days – 90 days</v>
       </c>
       <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
         <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>91 days – 180 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>5.25</v>
@@ -3817,21 +3507,21 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>181 days – less than 1 Year</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C8">
         <v>6.75</v>
@@ -3839,21 +3529,21 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>1 year 1 day – 370 days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>371 days – 390 days</v>
       </c>
       <c r="B10">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>7.25</v>
@@ -3861,62 +3551,51 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>391 days – 499 days</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>500 days – 3 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>3 years 1 day – 5 years</v>
       </c>
       <c r="B13">
+        <v>6.75</v>
+      </c>
+      <c r="C13">
         <v>7</v>
-      </c>
-      <c r="C13">
-        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>5 years 1 day – 10 years</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B15">
-        <v>6.75</v>
-      </c>
-      <c r="C15">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3943,10 +3622,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days – 14 days</v>
+        <v>7 days to 29 days</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>3.5</v>
@@ -3954,76 +3633,76 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days – 29 days</v>
+        <v>30 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.25</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 days – 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days – 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
         <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days – 180 days</v>
+        <v>181 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days – less than 1 Year</v>
+        <v>182 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>271 days to less than 1 year</v>
       </c>
       <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
         <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day – 370 days</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
         <v>6.75</v>
@@ -4031,57 +3710,57 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>371 days – 390 days</v>
+        <v>Above 1 year to less than 15 Months</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>391 days – 499 days</v>
+        <v>15 Months</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.8</v>
       </c>
       <c r="C11">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>500 days – 3 years</v>
+        <v>Above 15 months to less than 36 months</v>
       </c>
       <c r="B12">
-        <v>7.35</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>3 years 1 day – 5 years</v>
+        <v>36 months</v>
       </c>
       <c r="B13">
         <v>6.75</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5 years 1 day – 10 years</v>
+        <v>Above 36 months to 10 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>6.25</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -4,25 +4,27 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="HDFC Bank" sheetId="1" r:id="rId1"/>
-    <sheet name="ICICI Bank" sheetId="2" r:id="rId2"/>
-    <sheet name="Axis Bank" sheetId="3" r:id="rId3"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="PNB" sheetId="5" r:id="rId5"/>
-    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
-    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="Federal Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Bank of Baroda" sheetId="10" r:id="rId10"/>
-    <sheet name="Bank of India" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of Maharashtra" sheetId="12" r:id="rId12"/>
-    <sheet name="RBL Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="Indian Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Central Bank of India" sheetId="15" r:id="rId15"/>
-    <sheet name="Bandhan Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="PNB Housing Finance" sheetId="17" r:id="rId17"/>
-    <sheet name="KTDFC" sheetId="18" r:id="rId18"/>
-    <sheet name="LIC Housing Finance" sheetId="19" r:id="rId19"/>
-    <sheet name="Shriram Finance" sheetId="20" r:id="rId20"/>
+    <sheet name="SBI" sheetId="2" r:id="rId2"/>
+    <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
+    <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
+    <sheet name="PNB" sheetId="6" r:id="rId6"/>
+    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Indian Overseas Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Federal Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
+    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
+    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
+    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
+    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
+    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
+    <sheet name="Shriram Finance" sheetId="22" r:id="rId22"/>
   </sheets>
 </workbook>
 </file>
@@ -652,7 +654,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -672,7 +674,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7-14 Days*</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -683,7 +685,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-29 Days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -694,84 +696,84 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30-45 Days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46-60 Days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>61-90 Days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>91-120 Days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>121-179 Days</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>180-269 Days</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>270 Days to &lt; 1 Year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>1 Year</v>
       </c>
       <c r="B11">
         <v>6.5</v>
@@ -780,69 +782,229 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>444 Days</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>2 Years to &lt; 3 Years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>3 Years and above</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
         <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C14"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 29 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>30 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.25</v>
+      </c>
+      <c r="C3">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>182 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to less than 15 Months</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>15 Months</v>
+      </c>
+      <c r="B11">
+        <v>6.8</v>
+      </c>
+      <c r="C11">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 15 months to less than 36 months</v>
+      </c>
+      <c r="B12">
+        <v>6.4</v>
+      </c>
+      <c r="C12">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>36 months</v>
+      </c>
+      <c r="B13">
+        <v>6.75</v>
+      </c>
+      <c r="C13">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 36 months to 10 years</v>
+      </c>
+      <c r="B14">
+        <v>6.4</v>
+      </c>
+      <c r="C14">
+        <v>6.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -867,150 +1029,150 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>Above 10 years (MACAD only)</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1018,13 +1180,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1196,199 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1189,357 +1543,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 240 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>241 days to 364 days</v>
-      </c>
-      <c r="B7">
-        <v>6.05</v>
-      </c>
-      <c r="C7">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>18 months to 24 months</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
-      </c>
-      <c r="B11">
-        <v>7.2</v>
-      </c>
-      <c r="C11">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B13">
-        <v>6.7</v>
-      </c>
-      <c r="C13">
-        <v>7.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1566,7 +1569,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1577,123 +1580,123 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1704,6 +1707,198 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1725,134 +1920,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -1862,7 +2057,166 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -1966,9 +2320,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C11"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1988,281 +2342,117 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>7 days to 45 days</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>3.05</v>
       </c>
       <c r="C2">
-        <v>7.25</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2 years</v>
+        <v>46 days to 179 days</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="C3">
-        <v>7.25</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3 years</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="C4">
-        <v>7.25</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4 years</v>
+        <v>211 days to less than 1 year</v>
       </c>
       <c r="B5">
-        <v>6.75</v>
+        <v>5.9</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5 years</v>
+        <v>1 Year to less than 2 years</v>
       </c>
       <c r="B6">
+        <v>6.25</v>
+      </c>
+      <c r="C6">
         <v>6.75</v>
       </c>
-      <c r="C6">
-        <v>7</v>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B7">
+        <v>6.45</v>
+      </c>
+      <c r="C7">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B8">
+        <v>6.3</v>
+      </c>
+      <c r="C8">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>5 years and up to 10 years</v>
+      </c>
+      <c r="B9">
+        <v>6.05</v>
+      </c>
+      <c r="C9">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B10">
+        <v>6.55</v>
+      </c>
+      <c r="C10">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.8</v>
+      </c>
+      <c r="C11">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B4">
-        <v>6.75</v>
-      </c>
-      <c r="C4">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
-      </c>
-      <c r="C5">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B6">
-        <v>6.85</v>
-      </c>
-      <c r="C6">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B7">
-        <v>6.9</v>
-      </c>
-      <c r="C7">
-        <v>6.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 45 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 to 184 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
-      </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
-      </c>
-      <c r="B6">
-        <v>6.25</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
-      </c>
-      <c r="B7">
-        <v>6.3</v>
-      </c>
-      <c r="C7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
-      </c>
-      <c r="B8">
-        <v>6.45</v>
-      </c>
-      <c r="C8">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2289,6 +2479,181 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B4">
+        <v>6.75</v>
+      </c>
+      <c r="C4">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B5">
+        <v>6.8</v>
+      </c>
+      <c r="C5">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B6">
+        <v>6.85</v>
+      </c>
+      <c r="C6">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B7">
+        <v>6.9</v>
+      </c>
+      <c r="C7">
+        <v>6.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
         <v>12 Months</v>
       </c>
       <c r="B2">
@@ -2351,7 +2716,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2371,205 +2736,106 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 to 45 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>46 to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>91 to 184 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>185 to &lt; 1 Year</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>1 Year to &lt; 18 Months</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>18 Months to 2 Years</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
         <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2596,73 +2862,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 - 30 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 - 90 Days</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 Days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 Days</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -2673,18 +2939,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
         <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -2695,101 +2961,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>364 Days</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -2800,6 +3066,231 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -3064,187 +3555,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to 364 days</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
-      </c>
-      <c r="B10">
-        <v>6.75</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
-      </c>
-      <c r="B11">
-        <v>6.9</v>
-      </c>
-      <c r="C11">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.9</v>
-      </c>
-      <c r="C12">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
-      </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.65</v>
-      </c>
-      <c r="C14">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>61 Months and above</v>
-      </c>
-      <c r="B15">
-        <v>6.5</v>
-      </c>
-      <c r="C15">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3271,7 +3581,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -3282,7 +3592,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3293,7 +3603,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>46 days to 60 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -3304,7 +3614,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>61 days to 90 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -3315,51 +3625,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>270 days to 364 days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>1 Year to below 1 Year 6 Month</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -3370,57 +3680,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year 6 months to below 1 Year 7 months</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.9</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>1 Year 7 months to below 2 Years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>2 Years to 3 Years</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>Above 3 Years up to below 61 Months</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>61 Months and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3742,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3452,54 +3762,54 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days – 14 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days – 29 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 days – 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days – 90 days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days – 180 days</v>
+        <v>121 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
         <v>5.25</v>
@@ -3507,21 +3817,21 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days – less than 1 Year</v>
+        <v>181 days to 271 days</v>
       </c>
       <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
         <v>6.5</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>272 days to less than 12 months</v>
       </c>
       <c r="B8">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
         <v>6.75</v>
@@ -3529,21 +3839,21 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day – 370 days</v>
+        <v>12 months</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>371 days – 390 days</v>
+        <v>12 months 1 day to less than 18 months</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="C10">
         <v>7.25</v>
@@ -3551,51 +3861,62 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>391 days – 499 days</v>
+        <v>18 months</v>
       </c>
       <c r="B11">
+        <v>6.75</v>
+      </c>
+      <c r="C11">
         <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>500 days – 3 years</v>
+        <v>18 months 1 day to less than 24 months</v>
       </c>
       <c r="B12">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>7.6</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>3 years 1 day – 5 years</v>
+        <v>24 months to less than 36 months</v>
       </c>
       <c r="B13">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5 years 1 day – 10 years</v>
+        <v>36 months to less than 60 months</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>6.25</v>
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3622,10 +3943,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 29 days</v>
+        <v>7 days – 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C2">
         <v>3.5</v>
@@ -3633,76 +3954,76 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>30 days to 45 days</v>
+        <v>15 days – 29 days</v>
       </c>
       <c r="B3">
         <v>3.25</v>
       </c>
       <c r="C3">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30 days – 45 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days – 90 days</v>
       </c>
       <c r="B5">
         <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days</v>
+        <v>91 days – 180 days</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>182 days to 270 days</v>
+        <v>181 days – less than 1 Year</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>1 year 1 day – 370 days</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
         <v>6.75</v>
@@ -3710,57 +4031,57 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to less than 15 Months</v>
+        <v>371 days – 390 days</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>15 Months</v>
+        <v>391 days – 499 days</v>
       </c>
       <c r="B11">
-        <v>6.8</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 15 months to less than 36 months</v>
+        <v>500 days – 3 years</v>
       </c>
       <c r="B12">
-        <v>6.4</v>
+        <v>7.35</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>36 months</v>
+        <v>3 years 1 day – 5 years</v>
       </c>
       <c r="B13">
         <v>6.75</v>
       </c>
       <c r="C13">
-        <v>7.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 36 months to 10 years</v>
+        <v>5 years 1 day – 10 years</v>
       </c>
       <c r="B14">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.9</v>
+        <v>6.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -5,14 +5,14 @@
   <sheets>
     <sheet name="HDFC Bank" sheetId="1" r:id="rId1"/>
     <sheet name="SBI" sheetId="2" r:id="rId2"/>
-    <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
-    <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
-    <sheet name="PNB" sheetId="6" r:id="rId6"/>
-    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Indian Overseas Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Axis Bank" sheetId="3" r:id="rId3"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="4" r:id="rId4"/>
+    <sheet name="PNB" sheetId="5" r:id="rId5"/>
+    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
+    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="Indian Overseas Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="South Indian Bank" sheetId="10" r:id="rId10"/>
     <sheet name="Federal Bank" sheetId="11" r:id="rId11"/>
     <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
     <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
@@ -654,7 +654,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -674,18 +674,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7-14 Days*</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-29 Days</v>
+        <v>31 days to 90 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -696,140 +696,194 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30-45 Days</v>
+        <v>91 days to 99 days</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46-60 Days</v>
+        <v>100 daysto 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61-90 Days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>3.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91-120 Days</v>
+        <v>271 days to less than 1 year</v>
       </c>
       <c r="B7">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>121-179 Days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>2.9</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>3.4</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>180-269 Days</v>
+        <v>Above 1 year to 371 days</v>
       </c>
       <c r="B9">
-        <v>4.75</v>
+        <v>5.85</v>
       </c>
       <c r="C9">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
+        <v>372 days</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year</v>
+        <v>373 days to less than 18 months</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.05</v>
       </c>
       <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
       </c>
       <c r="B12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>444 Days</v>
+        <v>Above 18 months to less than 30 months</v>
       </c>
       <c r="B13">
-        <v>6.6</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>7.1</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
+        <v>30 months</v>
       </c>
       <c r="B14">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="C14">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3 Years and above</v>
+        <v>Above 30 months to less than 3 years</v>
       </c>
       <c r="B15">
-        <v>6.1</v>
+        <v>5.85</v>
       </c>
       <c r="C15">
-        <v>6.6</v>
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2716,7 +2770,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2736,106 +2790,205 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 to 45 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 to 90 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 to 184 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
         <v>6.5</v>
       </c>
-      <c r="C10">
+      <c r="C16">
         <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2862,73 +3015,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 - 14 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>15 - 30 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>31 - 45 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>46 - 90 Days</v>
       </c>
       <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>91 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>92 Days - 179 Days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>180 Days</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -2939,18 +3092,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>181 Days to 269 Days</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>270 Days</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -2961,101 +3114,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>271 Days to 363 Days</v>
       </c>
       <c r="B11">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>364 Days</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>365 Days to less than 15 Months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>15 Months - less than 18 Months</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>18 months - less than 2 years</v>
       </c>
       <c r="B15">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="C15">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>2 years- less than 3 years</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>3 years and above but less than 4 years</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>4 years and above but less than 5 years</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years to 10 years</v>
+        <v>5 years and above upto and inclusive of 10 years</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3066,231 +3219,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -3555,6 +3483,187 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to 364 days</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 Year to below 1 Year 6 Month</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 Year 6 months to below 1 Year 7 months</v>
+      </c>
+      <c r="B11">
+        <v>6.9</v>
+      </c>
+      <c r="C11">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 Year 7 months to below 2 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.9</v>
+      </c>
+      <c r="C12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 Years to 3 Years</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 3 Years up to below 61 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.65</v>
+      </c>
+      <c r="C14">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>61 Months and above</v>
+      </c>
+      <c r="B15">
+        <v>6.5</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3581,7 +3690,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -3592,7 +3701,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3603,7 +3712,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 60 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -3614,7 +3723,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>61 days to 90 days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -3625,51 +3734,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 180 days</v>
+        <v>121 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 210 days</v>
+        <v>181 days to 271 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>272 days to less than 12 months</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to 364 days</v>
+        <v>12 months</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
+        <v>12 months 1 day to less than 18 months</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -3680,57 +3789,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
+        <v>18 months</v>
       </c>
       <c r="B11">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="C11">
-        <v>7.4</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
+        <v>18 months 1 day to less than 24 months</v>
       </c>
       <c r="B12">
-        <v>6.9</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
+        <v>24 months to less than 36 months</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
+        <v>36 months to less than 60 months</v>
       </c>
       <c r="B14">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>7.15</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>61 Months and above</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B15">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -3741,6 +3850,176 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C14"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days – 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days – 29 days</v>
+      </c>
+      <c r="B3">
+        <v>3.25</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 days – 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.5</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days – 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days – 180 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days – less than 1 Year</v>
+      </c>
+      <c r="B7">
+        <v>6.5</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day – 370 days</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>371 days – 390 days</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>391 days – 499 days</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>500 days – 3 years</v>
+      </c>
+      <c r="B12">
+        <v>7.35</v>
+      </c>
+      <c r="C12">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3 years 1 day – 5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.75</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>5 years 1 day – 10 years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -3762,18 +4041,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7-14 Days*</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-29 Days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3784,134 +4063,135 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30-45 Days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>46-60 Days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>61-90 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>91-120 Days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>121-179 Days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>2.9</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>180-269 Days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>270 Days to &lt; 1 Year</v>
       </c>
       <c r="B10">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>444 Days</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>2 Years to &lt; 3 Years</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>3 Years and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3919,174 +4199,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days – 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days – 29 days</v>
-      </c>
-      <c r="B3">
-        <v>3.25</v>
-      </c>
-      <c r="C3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 days – 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days – 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days – 180 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days – less than 1 Year</v>
-      </c>
-      <c r="B7">
-        <v>6.5</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day – 370 days</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>371 days – 390 days</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>391 days – 499 days</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>500 days – 3 years</v>
-      </c>
-      <c r="B12">
-        <v>7.35</v>
-      </c>
-      <c r="C12">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>3 years 1 day – 5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.75</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>5 years 1 day – 10 years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>6.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -5,26 +5,27 @@
   <sheets>
     <sheet name="HDFC Bank" sheetId="1" r:id="rId1"/>
     <sheet name="SBI" sheetId="2" r:id="rId2"/>
-    <sheet name="Axis Bank" sheetId="3" r:id="rId3"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="PNB" sheetId="5" r:id="rId5"/>
-    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
-    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="Indian Overseas Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="South Indian Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Federal Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
-    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
-    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
-    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
-    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
-    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
-    <sheet name="Shriram Finance" sheetId="22" r:id="rId22"/>
+    <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
+    <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
+    <sheet name="PNB" sheetId="6" r:id="rId6"/>
+    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Indian Overseas Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="South Indian Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Federal Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of Baroda" sheetId="13" r:id="rId13"/>
+    <sheet name="Bank of India" sheetId="14" r:id="rId14"/>
+    <sheet name="Bank of Maharashtra" sheetId="15" r:id="rId15"/>
+    <sheet name="RBL Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
+    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
+    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
+    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
+    <sheet name="Shriram Finance" sheetId="23" r:id="rId23"/>
   </sheets>
 </workbook>
 </file>
@@ -654,6 +655,188 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7-14 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15-29 Days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30-45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3.5</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46-60 Days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>61-90 Days</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>91-120 Days</v>
+      </c>
+      <c r="B7">
+        <v>3.5</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>121-179 Days</v>
+      </c>
+      <c r="B8">
+        <v>2.9</v>
+      </c>
+      <c r="C8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>180-269 Days</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days to &lt; 1 Year</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
+      </c>
+      <c r="B12">
+        <v>6.4</v>
+      </c>
+      <c r="C12">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>444 Days</v>
+      </c>
+      <c r="B13">
+        <v>6.6</v>
+      </c>
+      <c r="C13">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 Years to &lt; 3 Years</v>
+      </c>
+      <c r="B14">
+        <v>6.4</v>
+      </c>
+      <c r="C14">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 Years and above</v>
+      </c>
+      <c r="B15">
+        <v>6.1</v>
+      </c>
+      <c r="C15">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -888,7 +1071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -1054,198 +1237,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1275,150 +1266,150 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>Above 10 years (MACAD only)</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1426,13 +1417,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1444,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1464,139 +1455,172 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1623,24 +1647,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -1648,109 +1672,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1761,6 +1785,165 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1948,165 +2131,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2133,134 +2157,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -2272,7 +2296,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2292,84 +2316,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>7.45</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>7.45</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>7.85</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>7.85</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>7.4</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months - 71 months</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>7.65</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>7.65</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>72 months - 84 months</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>7.4</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>120 months</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>7.4</v>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2513,6 +2592,110 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months - 23 months</v>
+      </c>
+      <c r="B2">
+        <v>7.45</v>
+      </c>
+      <c r="C2">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>24 months - 35 months</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>36 months - 47 months</v>
+      </c>
+      <c r="B4">
+        <v>7.85</v>
+      </c>
+      <c r="C4">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>48 months - 59 months</v>
+      </c>
+      <c r="B5">
+        <v>7.4</v>
+      </c>
+      <c r="C5">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>60 months - 71 months</v>
+      </c>
+      <c r="B6">
+        <v>7.65</v>
+      </c>
+      <c r="C6">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>72 months - 84 months</v>
+      </c>
+      <c r="B7">
+        <v>7.4</v>
+      </c>
+      <c r="C7">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>120 months</v>
+      </c>
+      <c r="B8">
+        <v>7.4</v>
+      </c>
+      <c r="C8">
+        <v>7.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2593,7 +2776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
@@ -2686,7 +2869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -2770,7 +2953,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2790,205 +2973,106 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 to 45 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>46 to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>91 to 184 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>185 to &lt; 1 Year</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>1 Year to &lt; 18 Months</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>18 Months to 2 Years</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
         <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3015,73 +3099,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 - 30 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 - 90 Days</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 Days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 Days</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -3092,18 +3176,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
         <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -3114,101 +3198,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>364 Days</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -3219,6 +3303,231 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -3483,187 +3792,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to 364 days</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
-      </c>
-      <c r="B10">
-        <v>6.75</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
-      </c>
-      <c r="B11">
-        <v>6.9</v>
-      </c>
-      <c r="C11">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.9</v>
-      </c>
-      <c r="C12">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
-      </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.65</v>
-      </c>
-      <c r="C14">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>61 Months and above</v>
-      </c>
-      <c r="B15">
-        <v>6.5</v>
-      </c>
-      <c r="C15">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3690,7 +3818,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -3701,7 +3829,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -3712,7 +3840,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>46 days to 60 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -3723,7 +3851,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>61 days to 90 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -3734,51 +3862,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>270 days to 364 days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>1 Year to below 1 Year 6 Month</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -3789,57 +3917,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year 6 months to below 1 Year 7 months</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.9</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>1 Year 7 months to below 2 Years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>2 Years to 3 Years</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>Above 3 Years up to below 61 Months</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>61 Months and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3850,6 +3978,187 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 120 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>121 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 271 days</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>272 days to less than 12 months</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B9">
+        <v>6.65</v>
+      </c>
+      <c r="C9">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>12 months 1 day to less than 18 months</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.75</v>
+      </c>
+      <c r="C11">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months 1 day to less than 24 months</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>24 months to less than 36 months</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>36 months to less than 60 months</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>7.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -4017,186 +4326,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7-14 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-29 Days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30-45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46-60 Days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61-90 Days</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91-120 Days</v>
-      </c>
-      <c r="B7">
-        <v>3.5</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>121-179 Days</v>
-      </c>
-      <c r="B8">
-        <v>2.9</v>
-      </c>
-      <c r="C8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>180-269 Days</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>444 Days</v>
-      </c>
-      <c r="B13">
-        <v>6.6</v>
-      </c>
-      <c r="C13">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
-      </c>
-      <c r="B14">
-        <v>6.4</v>
-      </c>
-      <c r="C14">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 Years and above</v>
-      </c>
-      <c r="B15">
-        <v>6.1</v>
-      </c>
-      <c r="C15">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -26,6 +26,13 @@
     <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
     <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
     <sheet name="Shriram Finance" sheetId="23" r:id="rId23"/>
+    <sheet name="Shivalik Small Finance Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Suryoday Small Finance Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="Utkarsh Small Finance Bank" sheetId="26" r:id="rId26"/>
+    <sheet name="Unity Small Finance Bank" sheetId="27" r:id="rId27"/>
+    <sheet name="Bajaj Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="Mahindra Finance" sheetId="29" r:id="rId29"/>
+    <sheet name="Shriram City Union Finance" sheetId="30" r:id="rId30"/>
   </sheets>
 </workbook>
 </file>
@@ -2951,6 +2958,938 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>3.75</v>
+      </c>
+      <c r="C3">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>6 months to less than 9 months</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>9 months to 12 months</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>12 months 1 day to 18 months</v>
+      </c>
+      <c r="B8">
+        <v>6.75</v>
+      </c>
+      <c r="C8">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>18 months  to 23 months</v>
+      </c>
+      <c r="B9">
+        <v>7.5</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>23 months 1 day to 27 months</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>27 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.5</v>
+      </c>
+      <c r="C11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months 1 day to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4.25</v>
+      </c>
+      <c r="C3">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>6 month 1 day</v>
+      </c>
+      <c r="B6">
+        <v>6.5</v>
+      </c>
+      <c r="C6">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Above 6 months 1 day to 9 months</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Above 9 months to less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>7.25</v>
+      </c>
+      <c r="C9">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to less than 18 months</v>
+      </c>
+      <c r="B10">
+        <v>7.25</v>
+      </c>
+      <c r="C10">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B11">
+        <v>7.6</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 18 months to 2 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 2 years to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>7.25</v>
+      </c>
+      <c r="C13">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>8.1</v>
+      </c>
+      <c r="C14">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to 3 years</v>
+      </c>
+      <c r="B15">
+        <v>7.25</v>
+      </c>
+      <c r="C15">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Above 3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.75</v>
+      </c>
+      <c r="C16">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B17">
+        <v>7.9</v>
+      </c>
+      <c r="C17">
+        <v>8.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Above 5 years to 10 years</v>
+      </c>
+      <c r="B18">
+        <v>7.25</v>
+      </c>
+      <c r="C18">
+        <v>7.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C12"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 45 days</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>4.5</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>181 days to 370 days</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>371 days to 665 days</v>
+      </c>
+      <c r="B6">
+        <v>7.25</v>
+      </c>
+      <c r="C6">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>666 days</v>
+      </c>
+      <c r="B7">
+        <v>8.1</v>
+      </c>
+      <c r="C7">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>667 days to 2 years</v>
+      </c>
+      <c r="B8">
+        <v>7.25</v>
+      </c>
+      <c r="C8">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2 years (730 days) to 3 years (1095 days)</v>
+      </c>
+      <c r="B9">
+        <v>7.5</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 3 years to less than 4 years</v>
+      </c>
+      <c r="B10">
+        <v>7.25</v>
+      </c>
+      <c r="C10">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>4 years (1461 days) to 5 years (1826 days)</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 5 years to 10 years</v>
+      </c>
+      <c r="B12">
+        <v>6.75</v>
+      </c>
+      <c r="C12">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C21"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.75</v>
+      </c>
+      <c r="C4">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 164 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>165 days to 6 months</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Above 6 months to 201 days</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>202 days to 364 days</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>7.5</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 year 1 day</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 1 year 1 day to 500 days</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>501 days</v>
+      </c>
+      <c r="B13">
+        <v>7.8</v>
+      </c>
+      <c r="C13">
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>502 days to 18 months</v>
+      </c>
+      <c r="B14">
+        <v>6.75</v>
+      </c>
+      <c r="C14">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 18 months to 700 days</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>701 days</v>
+      </c>
+      <c r="B16">
+        <v>6.75</v>
+      </c>
+      <c r="C16">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>702 days to 998 days</v>
+      </c>
+      <c r="B17">
+        <v>6.75</v>
+      </c>
+      <c r="C17">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>999 days to 34 months</v>
+      </c>
+      <c r="B18">
+        <v>6.75</v>
+      </c>
+      <c r="C18">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>34 months to 3 years</v>
+      </c>
+      <c r="B19">
+        <v>6.75</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Above 3 years to 5 years</v>
+      </c>
+      <c r="B20">
+        <v>6.75</v>
+      </c>
+      <c r="C20">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Above 5 years to 10 years</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months to 14 months</v>
+      </c>
+      <c r="B2">
+        <v>6.6</v>
+      </c>
+      <c r="C2">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months to 23 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>24 months to 60 months</v>
+      </c>
+      <c r="B4">
+        <v>6.95</v>
+      </c>
+      <c r="C4">
+        <v>6.95</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B2">
+        <v>6.6</v>
+      </c>
+      <c r="C2">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>24 months</v>
+      </c>
+      <c r="B3">
+        <v>6.85</v>
+      </c>
+      <c r="C3">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B4">
+        <v>6.85</v>
+      </c>
+      <c r="C4">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>36 months</v>
+      </c>
+      <c r="B5">
+        <v>7.4</v>
+      </c>
+      <c r="C5">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>42 months</v>
+      </c>
+      <c r="B6">
+        <v>7.4</v>
+      </c>
+      <c r="C6">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>48 months</v>
+      </c>
+      <c r="B7">
+        <v>7.45</v>
+      </c>
+      <c r="C7">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>60 months</v>
+      </c>
+      <c r="B8">
+        <v>7.45</v>
+      </c>
+      <c r="C8">
+        <v>7.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C10"/>
@@ -3073,6 +4012,88 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B2">
+        <v>6.85</v>
+      </c>
+      <c r="C2">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months (digital only)</v>
+      </c>
+      <c r="B3">
+        <v>7.1</v>
+      </c>
+      <c r="C3">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months – 23 months</v>
+      </c>
+      <c r="B4">
+        <v>7.05</v>
+      </c>
+      <c r="C4">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>24 months – 35 months</v>
+      </c>
+      <c r="B5">
+        <v>7.1</v>
+      </c>
+      <c r="C5">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>36 months – 60 months</v>
+      </c>
+      <c r="B6">
+        <v>7.5</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -20,18 +20,17 @@
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="South Indian Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Federal Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
-    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
-    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
-    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
-    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
-    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
-    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
+    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
+    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
+    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
+    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
+    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
   </sheets>
 </workbook>
 </file>
@@ -2143,242 +2142,6 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.9</v>
-      </c>
-      <c r="C2">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 90 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 days to 99 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.8</v>
-      </c>
-      <c r="C5">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>5.9</v>
-      </c>
-      <c r="C7">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
-      </c>
-      <c r="B9">
-        <v>5.85</v>
-      </c>
-      <c r="C9">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>372 days</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.05</v>
-      </c>
-      <c r="C11">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2543,6 +2306,198 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2786,150 +2741,150 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -2937,13 +2892,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2955,7 +2910,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2975,172 +2930,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3167,24 +3089,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -3192,109 +3114,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.25</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3305,6 +3227,198 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3326,7 +3440,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3337,320 +3451,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3677,134 +3599,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3815,165 +3737,6 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -4077,7 +3840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -4159,7 +3922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -16,21 +16,20 @@
     <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
     <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
     <sheet name="PNB" sheetId="13" r:id="rId13"/>
-    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
-    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
-    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
-    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
-    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Overseas Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Federal Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
+    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="Indian Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Central Bank of India" sheetId="23" r:id="rId23"/>
+    <sheet name="Bandhan Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="PNB Housing Finance" sheetId="25" r:id="rId25"/>
+    <sheet name="KTDFC" sheetId="26" r:id="rId26"/>
+    <sheet name="LIC Housing Finance" sheetId="27" r:id="rId27"/>
   </sheets>
 </workbook>
 </file>
@@ -1448,7 +1447,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -1459,7 +1458,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -1470,7 +1469,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 60 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -1481,7 +1480,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>61 days to 90 days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -1492,51 +1491,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 180 days</v>
+        <v>121 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 210 days</v>
+        <v>181 days to 271 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>272 days to less than 12 months</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to 364 days</v>
+        <v>12 months</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
+        <v>12 months 1 day to less than 18 months</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -1547,57 +1546,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
+        <v>18 months</v>
       </c>
       <c r="B11">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="C11">
-        <v>7.4</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
+        <v>18 months 1 day to less than 24 months</v>
       </c>
       <c r="B12">
-        <v>6.9</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
+        <v>24 months to less than 36 months</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
+        <v>36 months to less than 60 months</v>
       </c>
       <c r="B14">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>7.15</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>61 Months and above</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B15">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1608,6 +1607,176 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C14"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days – 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days – 29 days</v>
+      </c>
+      <c r="B3">
+        <v>3.25</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 days – 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.5</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days – 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days – 180 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days – less than 1 Year</v>
+      </c>
+      <c r="B7">
+        <v>6.5</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day – 370 days</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>371 days – 390 days</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>391 days – 499 days</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>500 days – 3 years</v>
+      </c>
+      <c r="B12">
+        <v>7.35</v>
+      </c>
+      <c r="C12">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3 years 1 day – 5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.75</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>5 years 1 day – 10 years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1629,18 +1798,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7-14 Days*</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-29 Days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -1651,134 +1820,135 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30-45 Days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>46-60 Days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>61-90 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>91-120 Days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>121-179 Days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>2.9</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>180-269 Days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>270 Days to &lt; 1 Year</v>
       </c>
       <c r="B10">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>444 Days</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>2 Years to &lt; 3 Years</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>3 Years and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1788,7 +1958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -1810,10 +1980,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days – 14 days</v>
+        <v>7 days to 29 days</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>3.5</v>
@@ -1821,76 +1991,76 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days – 29 days</v>
+        <v>30 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.25</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 days – 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days – 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
         <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days – 180 days</v>
+        <v>181 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days – less than 1 Year</v>
+        <v>182 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>271 days to less than 1 year</v>
       </c>
       <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
         <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day – 370 days</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
         <v>6.75</v>
@@ -1898,57 +2068,57 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>371 days – 390 days</v>
+        <v>Above 1 year to less than 15 Months</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>391 days – 499 days</v>
+        <v>15 Months</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.8</v>
       </c>
       <c r="C11">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>500 days – 3 years</v>
+        <v>Above 15 months to less than 36 months</v>
       </c>
       <c r="B12">
-        <v>7.35</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>3 years 1 day – 5 years</v>
+        <v>36 months</v>
       </c>
       <c r="B13">
         <v>6.75</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5 years 1 day – 10 years</v>
+        <v>Above 36 months to 10 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>6.25</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -1958,9 +2128,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1980,7 +2150,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7-14 Days*</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1991,195 +2161,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-29 Days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
       </c>
       <c r="C3">
         <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30-45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46-60 Days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61-90 Days</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91-120 Days</v>
-      </c>
-      <c r="B7">
-        <v>3.5</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>121-179 Days</v>
-      </c>
-      <c r="B8">
-        <v>2.9</v>
-      </c>
-      <c r="C8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>180-269 Days</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>444 Days</v>
-      </c>
-      <c r="B13">
-        <v>6.6</v>
-      </c>
-      <c r="C13">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
-      </c>
-      <c r="B14">
-        <v>6.4</v>
-      </c>
-      <c r="C14">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 Years and above</v>
-      </c>
-      <c r="B15">
-        <v>6.1</v>
-      </c>
-      <c r="C15">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 29 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>30 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.25</v>
-      </c>
-      <c r="C3">
-        <v>3.75</v>
       </c>
     </row>
     <row r="4">
@@ -2187,10 +2175,10 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
@@ -2198,37 +2186,37 @@
         <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
         <v>6</v>
-      </c>
-      <c r="C6">
-        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>182 days to 270 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -2250,62 +2238,84 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to less than 15 Months</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>15 Months</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 15 months to less than 36 months</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>36 months</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>7.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 36 months to 10 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.9</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2335,150 +2345,150 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -2486,13 +2496,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2718,7 +2728,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2738,172 +2748,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2930,24 +2907,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -2955,109 +2932,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.25</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3068,6 +3045,198 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3089,7 +3258,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3100,320 +3269,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3440,134 +3417,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3578,165 +3555,6 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -3840,7 +3658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3922,7 +3740,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -16,20 +16,22 @@
     <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
     <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
     <sheet name="PNB" sheetId="13" r:id="rId13"/>
-    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Overseas Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Federal Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
-    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="Indian Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Central Bank of India" sheetId="23" r:id="rId23"/>
-    <sheet name="Bandhan Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="PNB Housing Finance" sheetId="25" r:id="rId25"/>
-    <sheet name="KTDFC" sheetId="26" r:id="rId26"/>
-    <sheet name="LIC Housing Finance" sheetId="27" r:id="rId27"/>
+    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="South Indian Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Federal Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
+    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
+    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
+    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
+    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
+    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
+    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
   </sheets>
 </workbook>
 </file>
@@ -1447,7 +1449,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -1458,7 +1460,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -1469,7 +1471,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>46 days to 60 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -1480,7 +1482,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>61 days to 90 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -1491,51 +1493,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>270 days to 364 days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>1 Year to below 1 Year 6 Month</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -1546,57 +1548,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year 6 months to below 1 Year 7 months</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.9</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>1 Year 7 months to below 2 Years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>2 Years to 3 Years</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>Above 3 Years up to below 61 Months</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>61 Months and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1607,6 +1609,187 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 120 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>121 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 271 days</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>272 days to less than 12 months</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B9">
+        <v>6.65</v>
+      </c>
+      <c r="C9">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>12 months 1 day to less than 18 months</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.75</v>
+      </c>
+      <c r="C11">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months 1 day to less than 24 months</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>24 months to less than 36 months</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>36 months to less than 60 months</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>7.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -1776,7 +1959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1958,7 +2141,243 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -2124,390 +2543,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 30 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 179 days</v>
-      </c>
-      <c r="B6">
-        <v>4.25</v>
-      </c>
-      <c r="C6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>180 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.3</v>
-      </c>
-      <c r="C11">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>450 days</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2728,7 +2763,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2748,24 +2783,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2773,54 +2808,54 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
@@ -2828,64 +2863,289 @@
         <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>6.2</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>5.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2907,24 +3167,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2932,306 +3192,114 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3258,7 +3326,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3269,123 +3337,123 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3396,6 +3464,198 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3417,134 +3677,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3554,7 +3814,166 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -3658,7 +4077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3740,7 +4159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -9,29 +9,28 @@
     <sheet name="Unity Small Finance Bank" sheetId="4" r:id="rId4"/>
     <sheet name="Bajaj Finance" sheetId="5" r:id="rId5"/>
     <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
-    <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
-    <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="SBI" sheetId="9" r:id="rId9"/>
-    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="PNB" sheetId="13" r:id="rId13"/>
-    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="South Indian Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Federal Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
-    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
-    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
-    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
-    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
-    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
-    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
+    <sheet name="HDFC Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="SBI" sheetId="8" r:id="rId8"/>
+    <sheet name="ICICI Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Axis Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="PNB" sheetId="12" r:id="rId12"/>
+    <sheet name="IndusInd Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Overseas Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="South Indian Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
+    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
+    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
+    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
+    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
   </sheets>
 </workbook>
 </file>
@@ -584,7 +583,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -604,106 +603,205 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 to 45 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 to 90 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 to 184 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
         <v>6.5</v>
       </c>
-      <c r="C10">
+      <c r="C16">
         <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -730,73 +828,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 - 14 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>15 - 30 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>31 - 45 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>46 - 90 Days</v>
       </c>
       <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>91 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>92 Days - 179 Days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>180 Days</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -807,18 +905,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>181 Days to 269 Days</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>270 Days</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -829,101 +927,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>271 Days to 363 Days</v>
       </c>
       <c r="B11">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>364 Days</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>365 Days to less than 15 Months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>15 Months - less than 18 Months</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>18 months - less than 2 years</v>
       </c>
       <c r="B15">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="C15">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>2 years- less than 3 years</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>3 years and above but less than 4 years</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>4 years and above but less than 5 years</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years to 10 years</v>
+        <v>5 years and above upto and inclusive of 10 years</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -934,231 +1032,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1423,6 +1296,187 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to 364 days</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 Year to below 1 Year 6 Month</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 Year 6 months to below 1 Year 7 months</v>
+      </c>
+      <c r="B11">
+        <v>6.9</v>
+      </c>
+      <c r="C11">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 Year 7 months to below 2 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.9</v>
+      </c>
+      <c r="C12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 Years to 3 Years</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 3 Years up to below 61 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.65</v>
+      </c>
+      <c r="C14">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>61 Months and above</v>
+      </c>
+      <c r="B15">
+        <v>6.5</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1449,7 +1503,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -1460,7 +1514,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -1471,7 +1525,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 60 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -1482,7 +1536,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>61 days to 90 days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -1493,51 +1547,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 180 days</v>
+        <v>121 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 210 days</v>
+        <v>181 days to 271 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>272 days to less than 12 months</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to 364 days</v>
+        <v>12 months</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>6.65</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
+        <v>12 months 1 day to less than 18 months</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -1548,57 +1602,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
+        <v>18 months</v>
       </c>
       <c r="B11">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="C11">
-        <v>7.4</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
+        <v>18 months 1 day to less than 24 months</v>
       </c>
       <c r="B12">
-        <v>6.9</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
+        <v>24 months to less than 36 months</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
+        <v>36 months to less than 60 months</v>
       </c>
       <c r="B14">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>7.15</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>61 Months and above</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B15">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1609,6 +1663,176 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C14"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days – 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days – 29 days</v>
+      </c>
+      <c r="B3">
+        <v>3.25</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 days – 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.5</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days – 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days – 180 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days – less than 1 Year</v>
+      </c>
+      <c r="B7">
+        <v>6.5</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day – 370 days</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>371 days – 390 days</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>391 days – 499 days</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>500 days – 3 years</v>
+      </c>
+      <c r="B12">
+        <v>7.35</v>
+      </c>
+      <c r="C12">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3 years 1 day – 5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.75</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>5 years 1 day – 10 years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1630,18 +1854,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7-14 Days*</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-29 Days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -1652,134 +1876,135 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30-45 Days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>46-60 Days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>61-90 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>91-120 Days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>121-179 Days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>2.9</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>180-269 Days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>270 Days to &lt; 1 Year</v>
       </c>
       <c r="B10">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>444 Days</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>2 Years to &lt; 3 Years</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>3 Years and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1789,7 +2014,243 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -1811,10 +2272,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days – 14 days</v>
+        <v>7 days to 29 days</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>3.5</v>
@@ -1822,76 +2283,76 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days – 29 days</v>
+        <v>30 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.25</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 days – 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days – 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
         <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days – 180 days</v>
+        <v>181 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days – less than 1 Year</v>
+        <v>182 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>271 days to less than 1 year</v>
       </c>
       <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
         <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day – 370 days</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
         <v>6.75</v>
@@ -1899,57 +2360,57 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>371 days – 390 days</v>
+        <v>Above 1 year to less than 15 Months</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>391 days – 499 days</v>
+        <v>15 Months</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.8</v>
       </c>
       <c r="C11">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>500 days – 3 years</v>
+        <v>Above 15 months to less than 36 months</v>
       </c>
       <c r="B12">
-        <v>7.35</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>3 years 1 day – 5 years</v>
+        <v>36 months</v>
       </c>
       <c r="B13">
         <v>6.75</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5 years 1 day – 10 years</v>
+        <v>Above 36 months to 10 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>6.25</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -1959,9 +2420,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1981,7 +2442,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7-14 Days*</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1992,431 +2453,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-29 Days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
       </c>
       <c r="C3">
         <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30-45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46-60 Days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61-90 Days</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91-120 Days</v>
-      </c>
-      <c r="B7">
-        <v>3.5</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>121-179 Days</v>
-      </c>
-      <c r="B8">
-        <v>2.9</v>
-      </c>
-      <c r="C8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>180-269 Days</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>444 Days</v>
-      </c>
-      <c r="B13">
-        <v>6.6</v>
-      </c>
-      <c r="C13">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
-      </c>
-      <c r="B14">
-        <v>6.4</v>
-      </c>
-      <c r="C14">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 Years and above</v>
-      </c>
-      <c r="B15">
-        <v>6.1</v>
-      </c>
-      <c r="C15">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.9</v>
-      </c>
-      <c r="C2">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 90 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 days to 99 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.8</v>
-      </c>
-      <c r="C5">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>5.9</v>
-      </c>
-      <c r="C7">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
-      </c>
-      <c r="B9">
-        <v>5.85</v>
-      </c>
-      <c r="C9">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>372 days</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.05</v>
-      </c>
-      <c r="C11">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 29 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>30 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.25</v>
-      </c>
-      <c r="C3">
-        <v>3.75</v>
       </c>
     </row>
     <row r="4">
@@ -2424,10 +2467,10 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
@@ -2435,37 +2478,37 @@
         <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
         <v>6</v>
-      </c>
-      <c r="C6">
-        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>182 days to 270 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -2487,62 +2530,84 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to less than 15 Months</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>15 Months</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 15 months to less than 36 months</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>36 months</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>7.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 36 months to 10 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.9</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2786,150 +2851,150 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -2937,13 +3002,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2955,7 +3020,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2975,172 +3040,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3167,24 +3199,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -3192,109 +3224,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.25</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3305,6 +3337,198 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3326,7 +3550,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3337,320 +3561,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3677,134 +3709,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3815,165 +3847,6 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -4077,7 +3950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -4159,7 +4032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
@@ -4813,88 +4686,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months</v>
-      </c>
-      <c r="B2">
-        <v>6.85</v>
-      </c>
-      <c r="C2">
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months (digital only)</v>
-      </c>
-      <c r="B3">
-        <v>7.1</v>
-      </c>
-      <c r="C3">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months – 23 months</v>
-      </c>
-      <c r="B4">
-        <v>7.05</v>
-      </c>
-      <c r="C4">
-        <v>7.55</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>24 months – 35 months</v>
-      </c>
-      <c r="B5">
-        <v>7.1</v>
-      </c>
-      <c r="C5">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>36 months – 60 months</v>
-      </c>
-      <c r="B6">
-        <v>7.5</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -5129,7 +4920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -5264,4 +5055,130 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 45 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 to 184 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>185 to &lt; 1 Year</v>
+      </c>
+      <c r="B5">
+        <v>5.5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1 Year to &lt; 18 Months</v>
+      </c>
+      <c r="B6">
+        <v>6.25</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>18 Months to 2 Years</v>
+      </c>
+      <c r="B7">
+        <v>6.3</v>
+      </c>
+      <c r="C7">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2 Years 1 Day to 3 Years</v>
+      </c>
+      <c r="B8">
+        <v>6.45</v>
+      </c>
+      <c r="C8">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>3 Years 1 Day to 5 Years</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>5 Years 1 Day to 10 Years</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -9,17 +9,17 @@
     <sheet name="Unity Small Finance Bank" sheetId="4" r:id="rId4"/>
     <sheet name="Bajaj Finance" sheetId="5" r:id="rId5"/>
     <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
-    <sheet name="HDFC Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="SBI" sheetId="8" r:id="rId8"/>
-    <sheet name="ICICI Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Axis Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="PNB" sheetId="12" r:id="rId12"/>
-    <sheet name="IndusInd Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Overseas Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="South Indian Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
+    <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="SBI" sheetId="9" r:id="rId9"/>
+    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="PNB" sheetId="13" r:id="rId13"/>
+    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
     <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
     <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
     <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
@@ -583,7 +583,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -603,205 +603,106 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 to 45 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>46 to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>91 to 184 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>185 to &lt; 1 Year</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>1 Year to &lt; 18 Months</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>18 Months to 2 Years</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
         <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -828,73 +729,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 - 30 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 - 90 Days</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 Days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 Days</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -905,18 +806,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
         <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -927,101 +828,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>364 Days</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -1032,6 +933,231 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1296,187 +1422,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to 364 days</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
-      </c>
-      <c r="B10">
-        <v>6.75</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
-      </c>
-      <c r="B11">
-        <v>6.9</v>
-      </c>
-      <c r="C11">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.9</v>
-      </c>
-      <c r="C12">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
-      </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.65</v>
-      </c>
-      <c r="C14">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>61 Months and above</v>
-      </c>
-      <c r="B15">
-        <v>6.5</v>
-      </c>
-      <c r="C15">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1503,7 +1448,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -1514,7 +1459,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -1525,7 +1470,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>46 days to 60 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -1536,7 +1481,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>61 days to 90 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -1547,51 +1492,51 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>270 days to 364 days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>1 Year to below 1 Year 6 Month</v>
       </c>
       <c r="B10">
         <v>6.75</v>
@@ -1602,57 +1547,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year 6 months to below 1 Year 7 months</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.9</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>1 Year 7 months to below 2 Years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>2 Years to 3 Years</v>
       </c>
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>Above 3 Years up to below 61 Months</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>61 Months and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1663,6 +1608,187 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 120 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>121 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 271 days</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>272 days to less than 12 months</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B9">
+        <v>6.65</v>
+      </c>
+      <c r="C9">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>12 months 1 day to less than 18 months</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.75</v>
+      </c>
+      <c r="C11">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months 1 day to less than 24 months</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>24 months to less than 36 months</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>36 months to less than 60 months</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>7.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -1832,7 +1958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -2010,242 +2136,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.9</v>
-      </c>
-      <c r="C2">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 90 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 days to 99 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.8</v>
-      </c>
-      <c r="C5">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>5.9</v>
-      </c>
-      <c r="C7">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
-      </c>
-      <c r="B9">
-        <v>5.85</v>
-      </c>
-      <c r="C9">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>372 days</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.05</v>
-      </c>
-      <c r="C11">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4686,6 +4576,88 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B2">
+        <v>6.85</v>
+      </c>
+      <c r="C2">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months (digital only)</v>
+      </c>
+      <c r="B3">
+        <v>7.1</v>
+      </c>
+      <c r="C3">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months – 23 months</v>
+      </c>
+      <c r="B4">
+        <v>7.05</v>
+      </c>
+      <c r="C4">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>24 months – 35 months</v>
+      </c>
+      <c r="B5">
+        <v>7.1</v>
+      </c>
+      <c r="C5">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>36 months – 60 months</v>
+      </c>
+      <c r="B6">
+        <v>7.5</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -4920,7 +4892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -5055,130 +5027,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 45 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 to 184 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
-      </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
-      </c>
-      <c r="B6">
-        <v>6.25</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
-      </c>
-      <c r="B7">
-        <v>6.3</v>
-      </c>
-      <c r="C7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
-      </c>
-      <c r="B8">
-        <v>6.45</v>
-      </c>
-      <c r="C8">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -2264,15 +2264,15 @@
         <v>15 Months</v>
       </c>
       <c r="B11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="C11">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 15 months to less than 36 months</v>
+        <v>Above 15 months to less than 48 months</v>
       </c>
       <c r="B12">
         <v>6.4</v>
@@ -2283,18 +2283,18 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>36 months</v>
+        <v>48 months</v>
       </c>
       <c r="B13">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>7.25</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 36 months to 10 years</v>
+        <v>Above 48 months to 10 years</v>
       </c>
       <c r="B14">
         <v>6.4</v>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -729,7 +729,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -740,7 +740,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>15 days to 29 days</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>30 days to 45 days</v>
       </c>
       <c r="B4">
         <v>3.25</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>46 days to 60 days</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>61 days to 87 days</v>
       </c>
       <c r="B6">
         <v>4.75</v>
@@ -784,7 +784,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>88 days to 3 months 24 days</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>3 months 25 days to less than 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>4 months to less than 6 months</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>6 months to less than 9 months</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -828,7 +828,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>9 months to less than 1 year</v>
       </c>
       <c r="B11">
         <v>5.75</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>1 year to 1 year 10 days</v>
       </c>
       <c r="B12">
         <v>6.25</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>1 year 11 days to less than 13 months</v>
       </c>
       <c r="B13">
         <v>6.25</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>13 months to less than 15 months</v>
       </c>
       <c r="B14">
         <v>6.25</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>15 months to less than 18 months</v>
       </c>
       <c r="B15">
         <v>6.45</v>
@@ -883,35 +883,35 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>18 months to 2 years</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="19">
@@ -919,10 +919,10 @@
         <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -729,7 +729,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -740,7 +740,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 29 days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 days to 45 days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
         <v>3.25</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 60 days</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days to 87 days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
         <v>4.75</v>
@@ -784,7 +784,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days to 3 months 24 days</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days to less than 4 months</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months to less than 6 months</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months to less than 9 months</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -828,7 +828,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months to less than 1 year</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
         <v>5.75</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year to 1 year 10 days</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
         <v>6.25</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days to less than 13 months</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
         <v>6.25</v>
@@ -861,7 +861,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months to less than 15 months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
         <v>6.25</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months to less than 18 months</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
         <v>6.45</v>
@@ -883,35 +883,35 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 months to 2 years</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>6.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>6.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -919,10 +919,10 @@
         <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -20,17 +20,20 @@
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
-    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
-    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
-    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
-    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="South Indian Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Federal Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="Canara Bank" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Baroda" sheetId="21" r:id="rId21"/>
+    <sheet name="Bank of India" sheetId="22" r:id="rId22"/>
+    <sheet name="Bank of Maharashtra" sheetId="23" r:id="rId23"/>
+    <sheet name="RBL Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="IDBI Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="Indian Bank" sheetId="26" r:id="rId26"/>
+    <sheet name="Central Bank of India" sheetId="27" r:id="rId27"/>
+    <sheet name="Bandhan Bank" sheetId="28" r:id="rId28"/>
+    <sheet name="PNB Housing Finance" sheetId="29" r:id="rId29"/>
+    <sheet name="KTDFC" sheetId="30" r:id="rId30"/>
+    <sheet name="LIC Housing Finance" sheetId="31" r:id="rId31"/>
   </sheets>
 </workbook>
 </file>
@@ -2142,6 +2145,242 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2306,198 +2545,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2718,6 +2765,165 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 Days to 45 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 Days to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 Days to 179 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>180 Days to 269 Days</v>
+      </c>
+      <c r="B5">
+        <v>5.25</v>
+      </c>
+      <c r="C5">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>270 Days to less than 1 Year</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+      </c>
+      <c r="B7">
+        <v>6.25</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>444 Days*</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>555 Days*</v>
+      </c>
+      <c r="B9">
+        <v>6.6</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years &amp; above to less than 3 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 Years &amp; above to less than 5 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 Years &amp; above to 10 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2741,150 +2947,150 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>Above 10 years (MACAD only)</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -2892,13 +3098,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -2908,7 +3114,199 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2969,7 +3367,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -2980,7 +3378,7 @@
         <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
@@ -2991,7 +3389,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
@@ -3002,7 +3400,7 @@
         <v>5.25</v>
       </c>
       <c r="C8">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
@@ -3013,7 +3411,7 @@
         <v>6.2</v>
       </c>
       <c r="C9">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
@@ -3024,7 +3422,7 @@
         <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.15</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
@@ -3035,7 +3433,7 @@
         <v>5.25</v>
       </c>
       <c r="C11">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
@@ -3046,7 +3444,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
@@ -3057,363 +3455,12 @@
         <v>5</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 240 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>241 days to 364 days</v>
-      </c>
-      <c r="B7">
-        <v>6.05</v>
-      </c>
-      <c r="C7">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>18 months to 24 months</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
-      </c>
-      <c r="B11">
-        <v>7.2</v>
-      </c>
-      <c r="C11">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B13">
-        <v>6.7</v>
-      </c>
-      <c r="C13">
-        <v>7.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3440,7 +3487,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3451,123 +3498,123 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3578,6 +3625,413 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3599,134 +4053,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +4190,166 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -3764,7 +4377,7 @@
         <v>7.45</v>
       </c>
       <c r="C2">
-        <v>7.45</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3">
@@ -3775,7 +4388,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="4">
@@ -3786,7 +4399,7 @@
         <v>7.85</v>
       </c>
       <c r="C4">
-        <v>7.85</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5">
@@ -3797,7 +4410,7 @@
         <v>7.4</v>
       </c>
       <c r="C5">
-        <v>7.4</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="6">
@@ -3808,7 +4421,7 @@
         <v>7.65</v>
       </c>
       <c r="C6">
-        <v>7.65</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7">
@@ -3819,7 +4432,7 @@
         <v>7.4</v>
       </c>
       <c r="C7">
-        <v>7.4</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="8">
@@ -3830,187 +4443,12 @@
         <v>7.4</v>
       </c>
       <c r="C8">
-        <v>7.4</v>
+        <v>7.65</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B4">
-        <v>6.75</v>
-      </c>
-      <c r="C4">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
-      </c>
-      <c r="C5">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B6">
-        <v>6.85</v>
-      </c>
-      <c r="C6">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B7">
-        <v>6.9</v>
-      </c>
-      <c r="C7">
-        <v>6.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4159,6 +4597,181 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B4">
+        <v>6.75</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B5">
+        <v>6.8</v>
+      </c>
+      <c r="C5">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B6">
+        <v>6.85</v>
+      </c>
+      <c r="C6">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B7">
+        <v>6.9</v>
+      </c>
+      <c r="C7">
+        <v>7.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4438,7 +5051,7 @@
         <v>6.6</v>
       </c>
       <c r="C2">
-        <v>6.6</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
@@ -4449,7 +5062,7 @@
         <v>6.75</v>
       </c>
       <c r="C3">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
@@ -4460,7 +5073,7 @@
         <v>6.95</v>
       </c>
       <c r="C4">
-        <v>6.95</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -4472,7 +5085,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -4492,7 +5105,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>18 months</v>
+        <v>12 months</v>
       </c>
       <c r="B2">
         <v>6.6</v>
@@ -4503,18 +5116,18 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months</v>
+        <v>18 months</v>
       </c>
       <c r="B3">
+        <v>6.6</v>
+      </c>
+      <c r="C3">
         <v>6.85</v>
-      </c>
-      <c r="C3">
-        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 months</v>
+        <v>24 months</v>
       </c>
       <c r="B4">
         <v>6.85</v>
@@ -4525,18 +5138,18 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>36 months</v>
+        <v>30 months</v>
       </c>
       <c r="B5">
-        <v>7.4</v>
+        <v>6.85</v>
       </c>
       <c r="C5">
-        <v>7.75</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>42 months</v>
+        <v>36 months</v>
       </c>
       <c r="B6">
         <v>7.4</v>
@@ -4547,18 +5160,18 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>48 months</v>
+        <v>42 months</v>
       </c>
       <c r="B7">
-        <v>7.45</v>
+        <v>7.4</v>
       </c>
       <c r="C7">
-        <v>7.8</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>60 months</v>
+        <v>48 months</v>
       </c>
       <c r="B8">
         <v>7.45</v>
@@ -4567,9 +5180,20 @@
         <v>7.8</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>60 months</v>
+      </c>
+      <c r="B9">
+        <v>7.45</v>
+      </c>
+      <c r="C9">
+        <v>7.8</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -20,20 +20,19 @@
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="South Indian Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Federal Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="Canara Bank" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of Baroda" sheetId="21" r:id="rId21"/>
-    <sheet name="Bank of India" sheetId="22" r:id="rId22"/>
-    <sheet name="Bank of Maharashtra" sheetId="23" r:id="rId23"/>
-    <sheet name="RBL Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="IDBI Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="Indian Bank" sheetId="26" r:id="rId26"/>
-    <sheet name="Central Bank of India" sheetId="27" r:id="rId27"/>
-    <sheet name="Bandhan Bank" sheetId="28" r:id="rId28"/>
-    <sheet name="PNB Housing Finance" sheetId="29" r:id="rId29"/>
-    <sheet name="KTDFC" sheetId="30" r:id="rId30"/>
-    <sheet name="LIC Housing Finance" sheetId="31" r:id="rId31"/>
+    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
+    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
+    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
+    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
+    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
+    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
   </sheets>
 </workbook>
 </file>
@@ -2145,242 +2144,6 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.9</v>
-      </c>
-      <c r="C2">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 90 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 days to 99 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.8</v>
-      </c>
-      <c r="C5">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>5.9</v>
-      </c>
-      <c r="C7">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
-      </c>
-      <c r="B9">
-        <v>5.85</v>
-      </c>
-      <c r="C9">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>372 days</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.05</v>
-      </c>
-      <c r="C11">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2545,6 +2308,165 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 Days to 45 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 Days to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 Days to 179 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>180 Days to 269 Days</v>
+      </c>
+      <c r="B5">
+        <v>5.25</v>
+      </c>
+      <c r="C5">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>270 Days to less than 1 Year</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+      </c>
+      <c r="B7">
+        <v>6.25</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>444 Days*</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>555 Days*</v>
+      </c>
+      <c r="B9">
+        <v>6.6</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years &amp; above to less than 3 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 Years &amp; above to less than 5 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 Years &amp; above to 10 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2765,7 +2687,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2785,21 +2707,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -2807,29 +2729,29 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
         <v>5.5</v>
@@ -2840,84 +2762,117 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
         <v>6.25</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>444 Days*</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
         <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>555 Days*</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2947,164 +2902,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
         <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -3116,7 +3071,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3136,43 +3091,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -3180,128 +3135,95 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3328,24 +3250,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -3353,109 +3275,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3466,6 +3388,413 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3487,7 +3816,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3498,535 +3827,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4053,134 +3975,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -4191,165 +4113,6 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -4449,6 +4212,88 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4602,88 +4447,6 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -22,17 +22,7 @@
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
     <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
     <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
-    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
-    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
-    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
-    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
-    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
-    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
+    <sheet name="IDBI Bank" sheetId="20" r:id="rId20"/>
   </sheets>
 </workbook>
 </file>
@@ -2687,708 +2677,6 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 30 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 179 days</v>
-      </c>
-      <c r="B6">
-        <v>4.25</v>
-      </c>
-      <c r="C6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>180 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.3</v>
-      </c>
-      <c r="C11">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>450 days</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.6</v>
-      </c>
-      <c r="C2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 119 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>120 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to 364 days</v>
-      </c>
-      <c r="B8">
-        <v>5.25</v>
-      </c>
-      <c r="C8">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
-      </c>
-      <c r="B10">
-        <v>6.15</v>
-      </c>
-      <c r="C10">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
-      </c>
-      <c r="B11">
-        <v>5.25</v>
-      </c>
-      <c r="C11">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 5 years</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 240 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>241 days to 364 days</v>
-      </c>
-      <c r="B7">
-        <v>6.05</v>
-      </c>
-      <c r="C7">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>18 months to 24 months</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
-      </c>
-      <c r="B11">
-        <v>7.2</v>
-      </c>
-      <c r="C11">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B13">
-        <v>6.7</v>
-      </c>
-      <c r="C13">
-        <v>7.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3598,702 +2886,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months - 23 months</v>
-      </c>
-      <c r="B2">
-        <v>7.45</v>
-      </c>
-      <c r="C2">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>24 months - 35 months</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>36 months - 47 months</v>
-      </c>
-      <c r="B4">
-        <v>7.85</v>
-      </c>
-      <c r="C4">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>48 months - 59 months</v>
-      </c>
-      <c r="B5">
-        <v>7.4</v>
-      </c>
-      <c r="C5">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 months - 71 months</v>
-      </c>
-      <c r="B6">
-        <v>7.65</v>
-      </c>
-      <c r="C6">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>72 months - 84 months</v>
-      </c>
-      <c r="B7">
-        <v>7.4</v>
-      </c>
-      <c r="C7">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>120 months</v>
-      </c>
-      <c r="B8">
-        <v>7.4</v>
-      </c>
-      <c r="C8">
-        <v>7.65</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4442,99 +3034,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B4">
-        <v>6.75</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
-      </c>
-      <c r="C5">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B6">
-        <v>6.85</v>
-      </c>
-      <c r="C6">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B7">
-        <v>6.9</v>
-      </c>
-      <c r="C7">
-        <v>7.15</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -22,7 +22,17 @@
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
     <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
     <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="IDBI Bank" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
+    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
+    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
+    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
+    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
+    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
   </sheets>
 </workbook>
 </file>
@@ -2677,6 +2687,708 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.6</v>
+      </c>
+      <c r="C2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>3.75</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 119 days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>120 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to 364 days</v>
+      </c>
+      <c r="B8">
+        <v>5.25</v>
+      </c>
+      <c r="C8">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 2 years</v>
+      </c>
+      <c r="B10">
+        <v>6.15</v>
+      </c>
+      <c r="C10">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 2 years to 3 years</v>
+      </c>
+      <c r="B11">
+        <v>5.25</v>
+      </c>
+      <c r="C11">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above3 years to 5 years</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 5 years</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>5.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2886,6 +3598,702 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15-30 days</v>
+      </c>
+      <c r="B3">
+        <v>3.75</v>
+      </c>
+      <c r="C3">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.75</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 -59 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>60 - 90 days</v>
+      </c>
+      <c r="B6">
+        <v>4.5</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>91 -179 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 -270 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>271-364 days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 yr to less than 2 yrs</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 yr to less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 yr to less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years &amp; above up to 10 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months - 23 months</v>
+      </c>
+      <c r="B2">
+        <v>7.45</v>
+      </c>
+      <c r="C2">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>24 months - 35 months</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>36 months - 47 months</v>
+      </c>
+      <c r="B4">
+        <v>7.85</v>
+      </c>
+      <c r="C4">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>48 months - 59 months</v>
+      </c>
+      <c r="B5">
+        <v>7.4</v>
+      </c>
+      <c r="C5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>60 months - 71 months</v>
+      </c>
+      <c r="B6">
+        <v>7.65</v>
+      </c>
+      <c r="C6">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>72 months - 84 months</v>
+      </c>
+      <c r="B7">
+        <v>7.4</v>
+      </c>
+      <c r="C7">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>120 months</v>
+      </c>
+      <c r="B8">
+        <v>7.4</v>
+      </c>
+      <c r="C8">
+        <v>7.65</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3034,6 +4442,99 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B4">
+        <v>6.75</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B5">
+        <v>6.8</v>
+      </c>
+      <c r="C5">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B6">
+        <v>6.85</v>
+      </c>
+      <c r="C6">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B7">
+        <v>6.9</v>
+      </c>
+      <c r="C7">
+        <v>7.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -1430,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1505,18 +1505,18 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 210 days</v>
+        <v>121 days to 179 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>180 days</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -1527,84 +1527,106 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to 364 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B9">
+        <v>5.75</v>
+      </c>
+      <c r="C9">
         <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B10">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
+        <v>270 days to 364 days</v>
       </c>
       <c r="B11">
-        <v>6.9</v>
+        <v>6.25</v>
       </c>
       <c r="C11">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
+        <v>1 Year to below 1 Year 6 Month</v>
       </c>
       <c r="B12">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="C12">
-        <v>7.4</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 Years to 3 Years</v>
+        <v>1 Year 6 months to below 1 Year 7 months</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="C13">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
+        <v>1 Year 7 months to below 2 Years</v>
       </c>
       <c r="B14">
-        <v>6.65</v>
+        <v>6.9</v>
       </c>
       <c r="C14">
-        <v>7.15</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>2 Years to 3 Years</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Above 3 Years up to below 61 Months</v>
+      </c>
+      <c r="B16">
+        <v>6.65</v>
+      </c>
+      <c r="C16">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>61 Months and above</v>
       </c>
-      <c r="B15">
+      <c r="B17">
         <v>6.5</v>
       </c>
-      <c r="C15">
+      <c r="C17">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -1814,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C11"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days – 14 days</v>
+        <v>7 days – 29 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -1845,51 +1845,51 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days – 29 days</v>
+        <v>30 days – 45 days</v>
       </c>
       <c r="B3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 days – 45 days</v>
+        <v>46 days – 90 days</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days – 90 days</v>
+        <v>91 days – 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days – 180 days</v>
+        <v>181 days – less than 1 Year</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days – less than 1 Year</v>
+        <v>1 year – 370 days</v>
       </c>
       <c r="B7">
         <v>6.5</v>
@@ -1900,84 +1900,51 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>371 days – 499 days</v>
       </c>
       <c r="B8">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day – 370 days</v>
+        <v>500 days – 3 years</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>371 days – 390 days</v>
+        <v>3 years 1 day – 5 years</v>
       </c>
       <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
         <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>391 days – 499 days</v>
+        <v>5 years 1 day – 10 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>500 days – 3 years</v>
-      </c>
-      <c r="B12">
-        <v>7.35</v>
-      </c>
-      <c r="C12">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>3 years 1 day – 5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.75</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>5 years 1 day – 10 years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
         <v>6.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -25,14 +25,9 @@
     <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
     <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
     <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
-    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
-    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
-    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
-    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
-    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
+    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
   </sheets>
 </workbook>
 </file>
@@ -3219,165 +3214,6 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 240 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>241 days to 364 days</v>
-      </c>
-      <c r="B7">
-        <v>6.05</v>
-      </c>
-      <c r="C7">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>18 months to 24 months</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
-      </c>
-      <c r="B11">
-        <v>7.2</v>
-      </c>
-      <c r="C11">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B13">
-        <v>6.7</v>
-      </c>
-      <c r="C13">
-        <v>7.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3591,7 +3427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -3783,7 +3619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3938,351 +3774,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months - 23 months</v>
-      </c>
-      <c r="B2">
-        <v>7.45</v>
-      </c>
-      <c r="C2">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>24 months - 35 months</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>36 months - 47 months</v>
-      </c>
-      <c r="B4">
-        <v>7.85</v>
-      </c>
-      <c r="C4">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>48 months - 59 months</v>
-      </c>
-      <c r="B5">
-        <v>7.4</v>
-      </c>
-      <c r="C5">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 months - 71 months</v>
-      </c>
-      <c r="B6">
-        <v>7.65</v>
-      </c>
-      <c r="C6">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>72 months - 84 months</v>
-      </c>
-      <c r="B7">
-        <v>7.4</v>
-      </c>
-      <c r="C7">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>120 months</v>
-      </c>
-      <c r="B8">
-        <v>7.4</v>
-      </c>
-      <c r="C8">
-        <v>7.65</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4431,99 +3922,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B4">
-        <v>6.75</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
-      </c>
-      <c r="C5">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B6">
-        <v>6.85</v>
-      </c>
-      <c r="C6">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B7">
-        <v>6.9</v>
-      </c>
-      <c r="C7">
-        <v>7.15</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -11,23 +11,27 @@
     <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
     <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
     <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="SBI" sheetId="9" r:id="rId9"/>
-    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="PNB" sheetId="13" r:id="rId13"/>
-    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
-    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
+    <sheet name="ICICI Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Axis Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="PNB" sheetId="12" r:id="rId12"/>
+    <sheet name="IndusInd Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Overseas Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Federal Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
+    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
     <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
     <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
     <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
+    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
+    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
+    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
+    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
   </sheets>
 </workbook>
 </file>
@@ -580,7 +584,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -600,106 +604,205 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 to 45 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 to 90 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 to 184 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
         <v>6.5</v>
       </c>
-      <c r="C10">
+      <c r="C16">
         <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -726,73 +829,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 - 14 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>15 - 30 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>31 - 45 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>46 - 90 Days</v>
       </c>
       <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>91 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>92 Days - 179 Days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>180 Days</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -803,18 +906,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>181 Days to 269 Days</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>270 Days</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -825,101 +928,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>271 Days to 363 Days</v>
       </c>
       <c r="B11">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>364 Days</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>365 Days to less than 15 Months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>15 Months - less than 18 Months</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>18 months - less than 2 years</v>
       </c>
       <c r="B15">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="C15">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>2 years- less than 3 years</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>3 years and above but less than 4 years</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>4 years and above but less than 5 years</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years to 10 years</v>
+        <v>5 years and above upto and inclusive of 10 years</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -930,231 +1033,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1423,7 +1301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1626,7 +1504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1807,7 +1685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1944,7 +1822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -2126,7 +2004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -2296,7 +2174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2451,6 +2329,198 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2694,164 +2764,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
         <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -2863,7 +2933,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2883,43 +2953,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2927,128 +2997,95 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3075,24 +3112,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -3100,109 +3137,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3778,6 +3815,444 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months - 23 months</v>
+      </c>
+      <c r="B2">
+        <v>7.45</v>
+      </c>
+      <c r="C2">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>24 months - 35 months</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>36 months - 47 months</v>
+      </c>
+      <c r="B4">
+        <v>7.85</v>
+      </c>
+      <c r="C4">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>48 months - 59 months</v>
+      </c>
+      <c r="B5">
+        <v>7.4</v>
+      </c>
+      <c r="C5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>60 months - 71 months</v>
+      </c>
+      <c r="B6">
+        <v>7.65</v>
+      </c>
+      <c r="C6">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>72 months - 84 months</v>
+      </c>
+      <c r="B7">
+        <v>7.4</v>
+      </c>
+      <c r="C7">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>120 months</v>
+      </c>
+      <c r="B8">
+        <v>7.4</v>
+      </c>
+      <c r="C8">
+        <v>7.65</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B4">
+        <v>6.75</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B5">
+        <v>6.8</v>
+      </c>
+      <c r="C5">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B6">
+        <v>6.85</v>
+      </c>
+      <c r="C6">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B7">
+        <v>6.9</v>
+      </c>
+      <c r="C7">
+        <v>7.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C12"/>
@@ -4668,7 +5143,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -4688,51 +5163,51 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 45 days</v>
+        <v>7 to 45 Days</v>
       </c>
       <c r="B2">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 days to 179 days</v>
+        <v>46 to 90 Days</v>
       </c>
       <c r="B3">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>180 days to 210 days</v>
+        <v>91 to 184 Days</v>
       </c>
       <c r="B4">
-        <v>5.65</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>6.15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>211 days to less than 1 year</v>
+        <v>185 to &lt; 1 Year</v>
       </c>
       <c r="B5">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="C5">
-        <v>6.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to less than 2 years</v>
+        <v>1 Year to &lt; 18 Months</v>
       </c>
       <c r="B6">
         <v>6.25</v>
@@ -4743,62 +5218,51 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>18 Months to 2 Years</v>
       </c>
       <c r="B7">
-        <v>6.45</v>
+        <v>6.3</v>
       </c>
       <c r="C7">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="C8">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>5 years and up to 10 years</v>
+        <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>7.05</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year</v>
+        <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.8</v>
-      </c>
-      <c r="C11">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -11,27 +11,28 @@
     <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
     <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
     <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="ICICI Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Axis Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="PNB" sheetId="12" r:id="rId12"/>
-    <sheet name="IndusInd Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Overseas Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Federal Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
-    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
-    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
-    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
-    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
-    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
+    <sheet name="SBI" sheetId="9" r:id="rId9"/>
+    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="PNB" sheetId="13" r:id="rId13"/>
+    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
+    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
+    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
+    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
+    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
+    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
   </sheets>
 </workbook>
 </file>
@@ -584,7 +585,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -604,205 +605,106 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 to 45 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>46 to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>91 to 184 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>185 to &lt; 1 Year</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>1 Year to &lt; 18 Months</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>18 Months to 2 Years</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
         <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -829,73 +731,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 - 30 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 - 90 Days</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 Days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 Days</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -906,18 +808,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
         <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -928,101 +830,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>364 Days</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -1033,6 +935,231 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1301,7 +1428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1504,7 +1631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1685,7 +1812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1822,7 +1949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -2004,7 +2131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
@@ -2174,7 +2301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2329,198 +2456,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2764,164 +2699,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>Above 10 years (MACAD only)</v>
       </c>
       <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
         <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="C16">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -2933,7 +2868,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2953,43 +2888,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2997,95 +2932,128 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3112,24 +3080,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -3137,109 +3105,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -3250,6 +3218,165 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -3464,7 +3591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -3652,165 +3779,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3837,134 +3805,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3975,6 +3943,165 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -4078,7 +4205,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -4156,99 +4283,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B4">
-        <v>6.75</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
-      </c>
-      <c r="C5">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B6">
-        <v>6.85</v>
-      </c>
-      <c r="C6">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B7">
-        <v>6.9</v>
-      </c>
-      <c r="C7">
-        <v>7.15</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4397,6 +4431,99 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B4">
+        <v>6.75</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B5">
+        <v>6.8</v>
+      </c>
+      <c r="C5">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B6">
+        <v>6.85</v>
+      </c>
+      <c r="C6">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B7">
+        <v>6.9</v>
+      </c>
+      <c r="C7">
+        <v>7.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5143,7 +5270,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -5163,51 +5290,51 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 to 45 Days</v>
+        <v>7 days to 45 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 to 90 Days</v>
+        <v>46 days to 179 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 to 184 Days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>5.65</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
+        <v>211 days to less than 1 year</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
+        <v>1 Year to less than 2 years</v>
       </c>
       <c r="B6">
         <v>6.25</v>
@@ -5218,51 +5345,62 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B7">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="C7">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B8">
-        <v>6.45</v>
+        <v>6.3</v>
       </c>
       <c r="C8">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
+        <v>5 years and up to 10 years</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>6.05</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
+        <v>1 Year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.8</v>
+      </c>
+      <c r="C11">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -20,19 +20,20 @@
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
-    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
-    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
-    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
-    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
-    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
-    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
+    <sheet name="South Indian Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Federal Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="Canara Bank" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Baroda" sheetId="21" r:id="rId21"/>
+    <sheet name="Bank of India" sheetId="22" r:id="rId22"/>
+    <sheet name="Bank of Maharashtra" sheetId="23" r:id="rId23"/>
+    <sheet name="RBL Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="IDBI Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="Indian Bank" sheetId="26" r:id="rId26"/>
+    <sheet name="Central Bank of India" sheetId="27" r:id="rId27"/>
+    <sheet name="Bandhan Bank" sheetId="28" r:id="rId28"/>
+    <sheet name="PNB Housing Finance" sheetId="29" r:id="rId29"/>
+    <sheet name="KTDFC" sheetId="30" r:id="rId30"/>
+    <sheet name="LIC Housing Finance" sheetId="31" r:id="rId31"/>
   </sheets>
 </workbook>
 </file>
@@ -2133,6 +2134,242 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2297,165 +2534,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.25</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
-      </c>
-      <c r="B5">
-        <v>5.25</v>
-      </c>
-      <c r="C5">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
-      </c>
-      <c r="B7">
-        <v>6.25</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>444 Days*</v>
-      </c>
-      <c r="B8">
-        <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>555 Days*</v>
-      </c>
-      <c r="B9">
-        <v>6.6</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2676,7 +2754,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2696,21 +2774,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 Days to 45 Days*</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>46 Days to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -2718,29 +2796,29 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 Days to 179 Days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>180 Days to 269 Days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>270 Days to less than 1 Year</v>
       </c>
       <c r="B6">
         <v>5.5</v>
@@ -2751,117 +2829,84 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>444 Days*</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>555 Days*</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>2 Years &amp; above to less than 3 Years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>3 Years &amp; above to less than 5 Years</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>5 Years &amp; above to 10 Years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2891,164 +2936,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>Above 10 years (MACAD only)</v>
       </c>
       <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
         <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="C16">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -3060,7 +3105,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3080,43 +3125,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -3124,95 +3169,128 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3239,24 +3317,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -3264,109 +3342,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -3377,6 +3455,165 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -3591,7 +3828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -3779,165 +4016,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3964,134 +4042,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -4102,6 +4180,165 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -4201,88 +4438,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4436,6 +4591,88 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -20,20 +20,19 @@
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="South Indian Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Federal Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="Canara Bank" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of Baroda" sheetId="21" r:id="rId21"/>
-    <sheet name="Bank of India" sheetId="22" r:id="rId22"/>
-    <sheet name="Bank of Maharashtra" sheetId="23" r:id="rId23"/>
-    <sheet name="RBL Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="IDBI Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="Indian Bank" sheetId="26" r:id="rId26"/>
-    <sheet name="Central Bank of India" sheetId="27" r:id="rId27"/>
-    <sheet name="Bandhan Bank" sheetId="28" r:id="rId28"/>
-    <sheet name="PNB Housing Finance" sheetId="29" r:id="rId29"/>
-    <sheet name="KTDFC" sheetId="30" r:id="rId30"/>
-    <sheet name="LIC Housing Finance" sheetId="31" r:id="rId31"/>
+    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
+    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
+    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
+    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
+    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
+    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
   </sheets>
 </workbook>
 </file>
@@ -2134,242 +2133,6 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.9</v>
-      </c>
-      <c r="C2">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 90 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 days to 99 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.8</v>
-      </c>
-      <c r="C5">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>5.9</v>
-      </c>
-      <c r="C7">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
-      </c>
-      <c r="B9">
-        <v>5.85</v>
-      </c>
-      <c r="C9">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>372 days</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.05</v>
-      </c>
-      <c r="C11">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2534,6 +2297,165 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 Days to 45 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 Days to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 Days to 179 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>180 Days to 269 Days</v>
+      </c>
+      <c r="B5">
+        <v>5.25</v>
+      </c>
+      <c r="C5">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>270 Days to less than 1 Year</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+      </c>
+      <c r="B7">
+        <v>6.25</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>444 Days*</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>555 Days*</v>
+      </c>
+      <c r="B9">
+        <v>6.6</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years &amp; above to less than 3 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 Years &amp; above to less than 5 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 Years &amp; above to 10 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2754,7 +2676,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2774,21 +2696,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -2796,29 +2718,29 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
         <v>5.5</v>
@@ -2829,84 +2751,117 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
         <v>6.25</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>444 Days*</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
         <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>555 Days*</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2936,164 +2891,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
         <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -3105,7 +3060,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3125,43 +3080,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -3169,128 +3124,95 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3317,24 +3239,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -3342,109 +3264,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3455,6 +3377,413 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3476,7 +3805,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3487,535 +3816,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4042,134 +3964,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -4180,165 +4102,6 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -4438,6 +4201,88 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4591,88 +4436,6 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -20,7 +20,7 @@
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="South Indian Bank" sheetId="18" r:id="rId18"/>
     <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
     <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
     <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
@@ -2133,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2153,95 +2153,95 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 29 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>30 days to 45 days</v>
+        <v>31 days to 90 days</v>
       </c>
       <c r="B3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 99 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>100 daysto 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
         <v>6</v>
-      </c>
-      <c r="C6">
-        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>182 days to 270 days</v>
+        <v>271 days to less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 371 days</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to less than 15 Months</v>
+        <v>372 days</v>
       </c>
       <c r="B10">
         <v>6.4</v>
@@ -2252,51 +2252,117 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>15 Months</v>
+        <v>373 days to less than 18 months</v>
       </c>
       <c r="B11">
-        <v>6.6</v>
+        <v>6.05</v>
       </c>
       <c r="C11">
-        <v>7.1</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 15 months to less than 48 months</v>
+        <v>18 months</v>
       </c>
       <c r="B12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>48 months</v>
+        <v>Above 18 months to less than 30 months</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 48 months to 10 years</v>
+        <v>30 months</v>
       </c>
       <c r="B14">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="C14">
-        <v>6.9</v>
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -20,19 +20,12 @@
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="South Indian Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
     <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
     <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
     <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
     <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
-    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
-    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
-    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
-    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
-    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
+    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
   </sheets>
 </workbook>
 </file>
@@ -2133,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C14"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2153,95 +2146,95 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 29 days</v>
       </c>
       <c r="B2">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 90 days</v>
+        <v>30 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 days to 99 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 270 days</v>
+        <v>181 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>182 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>271 days to less than 1 year</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>6.35</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>372 days</v>
+        <v>Above 1 year to less than 15 Months</v>
       </c>
       <c r="B10">
         <v>6.4</v>
@@ -2252,117 +2245,51 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
+        <v>15 Months</v>
       </c>
       <c r="B11">
-        <v>6.05</v>
+        <v>6.6</v>
       </c>
       <c r="C11">
-        <v>6.55</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 months</v>
+        <v>Above 15 months to less than 48 months</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
+        <v>48 months</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>6.35</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>30 months</v>
+        <v>Above 48 months to 10 years</v>
       </c>
       <c r="B14">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3285,165 +3212,6 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 240 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>241 days to 364 days</v>
-      </c>
-      <c r="B7">
-        <v>6.05</v>
-      </c>
-      <c r="C7">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>18 months to 24 months</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
-      </c>
-      <c r="B11">
-        <v>7.2</v>
-      </c>
-      <c r="C11">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B13">
-        <v>6.7</v>
-      </c>
-      <c r="C13">
-        <v>7.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3653,702 +3421,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months - 23 months</v>
-      </c>
-      <c r="B2">
-        <v>7.45</v>
-      </c>
-      <c r="C2">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>24 months - 35 months</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>36 months - 47 months</v>
-      </c>
-      <c r="B4">
-        <v>7.85</v>
-      </c>
-      <c r="C4">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>48 months - 59 months</v>
-      </c>
-      <c r="B5">
-        <v>7.4</v>
-      </c>
-      <c r="C5">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 months - 71 months</v>
-      </c>
-      <c r="B6">
-        <v>7.65</v>
-      </c>
-      <c r="C6">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>72 months - 84 months</v>
-      </c>
-      <c r="B7">
-        <v>7.4</v>
-      </c>
-      <c r="C7">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>120 months</v>
-      </c>
-      <c r="B8">
-        <v>7.4</v>
-      </c>
-      <c r="C8">
-        <v>7.65</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4497,99 +3569,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B4">
-        <v>6.75</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
-      </c>
-      <c r="C5">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B6">
-        <v>6.85</v>
-      </c>
-      <c r="C6">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B7">
-        <v>6.9</v>
-      </c>
-      <c r="C7">
-        <v>7.15</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -25,7 +25,14 @@
     <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
     <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
     <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
-    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
+    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
+    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
+    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
   </sheets>
 </workbook>
 </file>
@@ -3212,6 +3219,165 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3421,6 +3587,702 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15-30 days</v>
+      </c>
+      <c r="B3">
+        <v>3.75</v>
+      </c>
+      <c r="C3">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.75</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 -59 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>60 - 90 days</v>
+      </c>
+      <c r="B6">
+        <v>4.5</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>91 -179 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 -270 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>271-364 days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 yr to less than 2 yrs</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 yr to less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 yr to less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years &amp; above up to 10 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months - 23 months</v>
+      </c>
+      <c r="B2">
+        <v>7.45</v>
+      </c>
+      <c r="C2">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>24 months - 35 months</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>36 months - 47 months</v>
+      </c>
+      <c r="B4">
+        <v>7.85</v>
+      </c>
+      <c r="C4">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>48 months - 59 months</v>
+      </c>
+      <c r="B5">
+        <v>7.4</v>
+      </c>
+      <c r="C5">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>60 months - 71 months</v>
+      </c>
+      <c r="B6">
+        <v>7.65</v>
+      </c>
+      <c r="C6">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>72 months - 84 months</v>
+      </c>
+      <c r="B7">
+        <v>7.4</v>
+      </c>
+      <c r="C7">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>120 months</v>
+      </c>
+      <c r="B8">
+        <v>7.4</v>
+      </c>
+      <c r="C8">
+        <v>7.65</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3569,6 +4431,99 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B4">
+        <v>6.75</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B5">
+        <v>6.8</v>
+      </c>
+      <c r="C5">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B6">
+        <v>6.85</v>
+      </c>
+      <c r="C6">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B7">
+        <v>6.9</v>
+      </c>
+      <c r="C7">
+        <v>7.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -9,30 +9,28 @@
     <sheet name="Unity Small Finance Bank" sheetId="4" r:id="rId4"/>
     <sheet name="Bajaj Finance" sheetId="5" r:id="rId5"/>
     <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
-    <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
-    <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="SBI" sheetId="9" r:id="rId9"/>
-    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="PNB" sheetId="13" r:id="rId13"/>
-    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
-    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
-    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
-    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
-    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
-    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
-    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
+    <sheet name="HDFC Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="SBI" sheetId="8" r:id="rId8"/>
+    <sheet name="ICICI Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Axis Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="PNB" sheetId="12" r:id="rId12"/>
+    <sheet name="IndusInd Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Overseas Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
+    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
+    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
+    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
+    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
   </sheets>
 </workbook>
 </file>
@@ -585,7 +583,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -605,106 +603,205 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 to 45 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 to 90 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 to 184 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
         <v>6.5</v>
       </c>
-      <c r="C10">
+      <c r="C16">
         <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -731,73 +828,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 - 14 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>15 - 30 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>31 - 45 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>46 - 90 Days</v>
       </c>
       <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>91 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>92 Days - 179 Days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>180 Days</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -808,18 +905,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>181 Days to 269 Days</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>270 Days</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -830,101 +927,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>271 Days to 363 Days</v>
       </c>
       <c r="B11">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>364 Days</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>365 Days to less than 15 Months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>15 Months - less than 18 Months</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>18 months - less than 2 years</v>
       </c>
       <c r="B15">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="C15">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>2 years- less than 3 years</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>3 years and above but less than 4 years</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>4 years and above but less than 5 years</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years to 10 years</v>
+        <v>5 years and above upto and inclusive of 10 years</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -935,231 +1032,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1428,7 +1300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1631,7 +1503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1812,7 +1684,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1949,7 +1821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -2131,177 +2003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 29 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>30 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.25</v>
-      </c>
-      <c r="C3">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.25</v>
-      </c>
-      <c r="C4">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>182 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to less than 15 Months</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>15 Months</v>
-      </c>
-      <c r="B11">
-        <v>6.6</v>
-      </c>
-      <c r="C11">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 15 months to less than 48 months</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>48 months</v>
-      </c>
-      <c r="B13">
-        <v>6.7</v>
-      </c>
-      <c r="C13">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 48 months to 10 years</v>
-      </c>
-      <c r="B14">
-        <v>6.4</v>
-      </c>
-      <c r="C14">
-        <v>6.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2456,6 +2158,390 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2676,7 +2762,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2696,24 +2782,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2721,54 +2807,54 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
@@ -2776,97 +2862,438 @@
         <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
         <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -2888,90 +3315,90 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 to 29 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>30 to 45 days</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>46 to 90 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>91 to 120 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>121 to 180 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>181 days to less than 9 months</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>9 months to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
@@ -2979,26 +3406,26 @@
         <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>444 days (Ind Secure Product)</v>
       </c>
       <c r="B12">
         <v>6.6</v>
@@ -3009,40 +3436,40 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>555 days (Ind Green Product)</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="C15">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>5 years</v>
       </c>
       <c r="B16">
         <v>6</v>
@@ -3058,7 +3485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3080,62 +3507,62 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
         <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -3146,68 +3573,68 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3217,7 +3644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3239,73 +3666,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -3316,7 +3743,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -3327,7 +3754,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -3338,35 +3765,35 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3376,732 +3803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.25</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -4205,7 +3907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -4283,6 +3985,99 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B4">
+        <v>6.75</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B5">
+        <v>6.8</v>
+      </c>
+      <c r="C5">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B6">
+        <v>6.85</v>
+      </c>
+      <c r="C6">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B7">
+        <v>6.9</v>
+      </c>
+      <c r="C7">
+        <v>7.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4431,99 +4226,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B4">
-        <v>6.75</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
-      </c>
-      <c r="C5">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B6">
-        <v>6.85</v>
-      </c>
-      <c r="C6">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B7">
-        <v>6.9</v>
-      </c>
-      <c r="C7">
-        <v>7.15</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4952,88 +4654,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months</v>
-      </c>
-      <c r="B2">
-        <v>6.85</v>
-      </c>
-      <c r="C2">
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months (digital only)</v>
-      </c>
-      <c r="B3">
-        <v>7.1</v>
-      </c>
-      <c r="C3">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months – 23 months</v>
-      </c>
-      <c r="B4">
-        <v>7.05</v>
-      </c>
-      <c r="C4">
-        <v>7.55</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>24 months – 35 months</v>
-      </c>
-      <c r="B5">
-        <v>7.1</v>
-      </c>
-      <c r="C5">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>36 months – 60 months</v>
-      </c>
-      <c r="B6">
-        <v>7.5</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -5268,7 +4888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -5403,4 +5023,130 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 45 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 to 184 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>185 to &lt; 1 Year</v>
+      </c>
+      <c r="B5">
+        <v>5.5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1 Year to &lt; 18 Months</v>
+      </c>
+      <c r="B6">
+        <v>6.25</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>18 Months to 2 Years</v>
+      </c>
+      <c r="B7">
+        <v>6.3</v>
+      </c>
+      <c r="C7">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2 Years 1 Day to 3 Years</v>
+      </c>
+      <c r="B8">
+        <v>6.45</v>
+      </c>
+      <c r="C8">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>3 Years 1 Day to 5 Years</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>5 Years 1 Day to 10 Years</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -9,28 +9,29 @@
     <sheet name="Unity Small Finance Bank" sheetId="4" r:id="rId4"/>
     <sheet name="Bajaj Finance" sheetId="5" r:id="rId5"/>
     <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
-    <sheet name="HDFC Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="SBI" sheetId="8" r:id="rId8"/>
-    <sheet name="ICICI Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Axis Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="PNB" sheetId="12" r:id="rId12"/>
-    <sheet name="IndusInd Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Overseas Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
-    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
-    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
-    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
-    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
+    <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="SBI" sheetId="9" r:id="rId9"/>
+    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="PNB" sheetId="13" r:id="rId13"/>
+    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
+    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
+    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
+    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
+    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
+    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
   </sheets>
 </workbook>
 </file>
@@ -583,7 +584,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -603,205 +604,106 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 to 45 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>46 to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>91 to 184 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>185 to &lt; 1 Year</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>1 Year to &lt; 18 Months</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>18 Months to 2 Years</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
         <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -828,73 +730,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 - 30 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 - 90 Days</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 Days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 Days</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -905,18 +807,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
         <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -927,101 +829,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>364 Days</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -1032,6 +934,231 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1300,7 +1427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1503,7 +1630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1684,7 +1811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1821,7 +1948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -2003,7 +2130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2158,198 +2285,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2379,164 +2314,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>Above 10 years (MACAD only)</v>
       </c>
       <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
         <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="C16">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -2762,7 +2697,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2782,43 +2717,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2826,95 +2761,128 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2941,24 +2909,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2966,109 +2934,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -3079,6 +3047,165 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -3293,7 +3420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -3481,165 +3608,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3666,134 +3634,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3804,6 +3772,165 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.25</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -3907,7 +4034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3989,7 +4116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
@@ -4654,6 +4781,88 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B2">
+        <v>6.85</v>
+      </c>
+      <c r="C2">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months (digital only)</v>
+      </c>
+      <c r="B3">
+        <v>7.1</v>
+      </c>
+      <c r="C3">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months – 23 months</v>
+      </c>
+      <c r="B4">
+        <v>7.05</v>
+      </c>
+      <c r="C4">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>24 months – 35 months</v>
+      </c>
+      <c r="B5">
+        <v>7.1</v>
+      </c>
+      <c r="C5">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>36 months – 60 months</v>
+      </c>
+      <c r="B6">
+        <v>7.5</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -4888,7 +5097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -5023,130 +5232,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 45 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 to 184 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
-      </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
-      </c>
-      <c r="B6">
-        <v>6.25</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
-      </c>
-      <c r="B7">
-        <v>6.3</v>
-      </c>
-      <c r="C7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
-      </c>
-      <c r="B8">
-        <v>6.45</v>
-      </c>
-      <c r="C8">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -3895,10 +3895,10 @@
         <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.25</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -19,19 +19,18 @@
     <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
-    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
-    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
-    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
-    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
-    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
+    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
+    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
+    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
+    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
+    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
   </sheets>
 </workbook>
 </file>
@@ -1950,188 +1949,6 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7-14 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-29 Days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30-45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46-60 Days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61-90 Days</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91-120 Days</v>
-      </c>
-      <c r="B7">
-        <v>3.5</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>121-179 Days</v>
-      </c>
-      <c r="B8">
-        <v>2.9</v>
-      </c>
-      <c r="C8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>180-269 Days</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>444 Days</v>
-      </c>
-      <c r="B13">
-        <v>6.6</v>
-      </c>
-      <c r="C13">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
-      </c>
-      <c r="B14">
-        <v>6.4</v>
-      </c>
-      <c r="C14">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 Years and above</v>
-      </c>
-      <c r="B15">
-        <v>6.1</v>
-      </c>
-      <c r="C15">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2285,6 +2102,198 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2314,164 +2323,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
         <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -2697,7 +2706,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2717,43 +2726,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2761,128 +2770,95 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2909,24 +2885,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -2934,109 +2910,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3047,6 +3023,413 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3068,7 +3451,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3079,535 +3462,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3634,134 +3610,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3772,165 +3748,6 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -4034,7 +3851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -4116,7 +3933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -19,18 +19,19 @@
     <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
-    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
-    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
-    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
-    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
+    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
+    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
+    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
+    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
+    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
   </sheets>
 </workbook>
 </file>
@@ -1949,6 +1950,188 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7-14 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15-29 Days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30-45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3.5</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46-60 Days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>61-90 Days</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>91-120 Days</v>
+      </c>
+      <c r="B7">
+        <v>3.5</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>121-179 Days</v>
+      </c>
+      <c r="B8">
+        <v>2.9</v>
+      </c>
+      <c r="C8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>180-269 Days</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days to &lt; 1 Year</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
+      </c>
+      <c r="B12">
+        <v>6.4</v>
+      </c>
+      <c r="C12">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>444 Days</v>
+      </c>
+      <c r="B13">
+        <v>6.6</v>
+      </c>
+      <c r="C13">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 Years to &lt; 3 Years</v>
+      </c>
+      <c r="B14">
+        <v>6.4</v>
+      </c>
+      <c r="C14">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 Years and above</v>
+      </c>
+      <c r="B15">
+        <v>6.1</v>
+      </c>
+      <c r="C15">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2102,198 +2285,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2323,164 +2314,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>Above 10 years (MACAD only)</v>
       </c>
       <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
         <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="C16">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -2706,7 +2697,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2726,43 +2717,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2770,95 +2761,128 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2885,24 +2909,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2910,109 +2934,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -3023,6 +3047,165 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -3237,7 +3420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -3425,165 +3608,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3610,134 +3634,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3748,6 +3772,165 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -3851,7 +4034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3933,7 +4116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -5054,7 +5054,7 @@
         <v>6.5</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="18">

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -2605,10 +2605,10 @@
         <v>18 months</v>
       </c>
       <c r="B11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="C11">
-        <v>7.75</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
@@ -2671,10 +2671,10 @@
         <v>5 years</v>
       </c>
       <c r="B17">
-        <v>7.9</v>
+        <v>8.25</v>
       </c>
       <c r="C17">
-        <v>8.05</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18">

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -710,7 +710,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C24"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -730,205 +730,260 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>45 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>10 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>11 days &lt; 13 months</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B11">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>14 days</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>29 days</v>
       </c>
       <c r="B15">
-        <v>6.45</v>
+        <v>3.5</v>
       </c>
       <c r="C15">
-        <v>6.95</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>60 days</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>24 days</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>25 days &lt; 4 months</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>4.25</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years to 10 years</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B20">
+        <v>6.6</v>
+      </c>
+      <c r="C20">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B21">
+        <v>6.6</v>
+      </c>
+      <c r="C21">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B22">
+        <v>6.6</v>
+      </c>
+      <c r="C22">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B23">
+        <v>6.6</v>
+      </c>
+      <c r="C23">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B24">
+        <v>6.25</v>
+      </c>
+      <c r="C24">
+        <v>6.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C24"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -16,22 +16,21 @@
     <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
     <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
     <sheet name="PNB" sheetId="13" r:id="rId13"/>
-    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
-    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
-    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
-    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
-    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
-    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
+    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Overseas Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
+    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
+    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
+    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
+    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
   </sheets>
 </workbook>
 </file>
@@ -710,7 +709,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -730,260 +729,205 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>45 days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>61 days - 87 days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>10 days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>11 days &lt; 13 months</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to 10 years</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>14 days</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
-        <v>3.5</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>29 days</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
-        <v>3.5</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>3.5</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>60 days</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>4.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>24 days</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>25 days &lt; 4 months</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>4.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B20">
-        <v>6.6</v>
-      </c>
-      <c r="C20">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B21">
-        <v>6.6</v>
-      </c>
-      <c r="C21">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B22">
-        <v>6.6</v>
-      </c>
-      <c r="C22">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B23">
-        <v>6.6</v>
-      </c>
-      <c r="C23">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B24">
-        <v>6.25</v>
-      </c>
-      <c r="C24">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1484,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1504,7 +1448,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.25</v>
@@ -1515,7 +1459,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -1526,7 +1470,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 60 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -1537,7 +1481,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>61 days to 90 days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B5">
         <v>4.75</v>
@@ -1548,144 +1492,259 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 120 days</v>
+        <v>121 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>121 days to 179 days</v>
+        <v>181 days to 271 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 days</v>
+        <v>272 days to less than 12 months</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>181 days to 210 days</v>
+        <v>12 months</v>
       </c>
       <c r="B9">
-        <v>5.75</v>
+        <v>6.65</v>
       </c>
       <c r="C9">
-        <v>6.25</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>211 days to 269 days</v>
+        <v>12 months 1 day to less than 18 months</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="C10">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>270 days to 364 days</v>
+        <v>18 months</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="C11">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
+        <v>18 months 1 day to less than 24 months</v>
       </c>
       <c r="B12">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>7.25</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
+        <v>24 months to less than 36 months</v>
       </c>
       <c r="B13">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
+        <v>36 months to less than 60 months</v>
       </c>
       <c r="B14">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>7.4</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2 Years to 3 Years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="C15">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
-      </c>
-      <c r="B16">
-        <v>6.65</v>
-      </c>
-      <c r="C16">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>61 Months and above</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C11"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days – 29 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>30 days – 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days – 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days – 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days – less than 1 Year</v>
+      </c>
+      <c r="B6">
+        <v>6.5</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1 year – 370 days</v>
+      </c>
+      <c r="B7">
+        <v>6.5</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>371 days – 499 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>500 days – 3 years</v>
+      </c>
+      <c r="B9">
+        <v>7.25</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>3 years 1 day – 5 years</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>5 years 1 day – 10 years</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1707,18 +1766,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7-14 Days*</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-29 Days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -1729,134 +1788,135 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>30-45 Days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 120 days</v>
+        <v>46-60 Days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>121 days to 180 days</v>
+        <v>61-90 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 271 days</v>
+        <v>91-120 Days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>6.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
+        <v>121-179 Days</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>2.9</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>12 months</v>
+        <v>180-269 Days</v>
       </c>
       <c r="B9">
-        <v>6.65</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>7.15</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
+        <v>270 Days to &lt; 1 Year</v>
       </c>
       <c r="B10">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>7.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>18 months</v>
+        <v>1 Year</v>
       </c>
       <c r="B11">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.4</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
+        <v>444 Days</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
+        <v>2 Years to &lt; 3 Years</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C14">
-        <v>7.75</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>60 months to 120 months</v>
+        <v>3 Years and above</v>
       </c>
       <c r="B15">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="C15">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1866,326 +1926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days – 29 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>30 days – 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days – 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days – 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days – less than 1 Year</v>
-      </c>
-      <c r="B6">
-        <v>6.5</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>1 year – 370 days</v>
-      </c>
-      <c r="B7">
-        <v>6.5</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>371 days – 499 days</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>500 days – 3 years</v>
-      </c>
-      <c r="B9">
-        <v>7.25</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>3 years 1 day – 5 years</v>
-      </c>
-      <c r="B10">
-        <v>6.75</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>5 years 1 day – 10 years</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7-14 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-29 Days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30-45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3.5</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46-60 Days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61-90 Days</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91-120 Days</v>
-      </c>
-      <c r="B7">
-        <v>3.5</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>121-179 Days</v>
-      </c>
-      <c r="B8">
-        <v>2.9</v>
-      </c>
-      <c r="C8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>180-269 Days</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>444 Days</v>
-      </c>
-      <c r="B13">
-        <v>6.6</v>
-      </c>
-      <c r="C13">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
-      </c>
-      <c r="B14">
-        <v>6.4</v>
-      </c>
-      <c r="C14">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 Years and above</v>
-      </c>
-      <c r="B15">
-        <v>6.1</v>
-      </c>
-      <c r="C15">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2340,6 +2081,198 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2369,164 +2302,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
         <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -2752,7 +2685,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2772,43 +2705,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2816,128 +2749,95 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2964,24 +2864,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -2989,109 +2889,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3102,6 +3002,413 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3123,7 +3430,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3134,535 +3441,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3689,134 +3589,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3827,165 +3727,6 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -4089,7 +3830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -4171,7 +3912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -8,29 +8,28 @@
     <sheet name="Utkarsh Small Finance Bank" sheetId="3" r:id="rId3"/>
     <sheet name="Unity Small Finance Bank" sheetId="4" r:id="rId4"/>
     <sheet name="Bajaj Finance" sheetId="5" r:id="rId5"/>
-    <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
-    <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
-    <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="SBI" sheetId="9" r:id="rId9"/>
-    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="PNB" sheetId="13" r:id="rId13"/>
-    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Overseas Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
-    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
-    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
-    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
-    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="HDFC Bank" sheetId="6" r:id="rId6"/>
+    <sheet name="SBI" sheetId="7" r:id="rId7"/>
+    <sheet name="ICICI Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="Axis Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="PNB" sheetId="11" r:id="rId11"/>
+    <sheet name="IndusInd Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="Yes Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="IDFC First Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Indian Overseas Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Canara Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Bank of Baroda" sheetId="17" r:id="rId17"/>
+    <sheet name="Bank of India" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of Maharashtra" sheetId="19" r:id="rId19"/>
+    <sheet name="RBL Bank" sheetId="20" r:id="rId20"/>
+    <sheet name="IDBI Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="Indian Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Central Bank of India" sheetId="23" r:id="rId23"/>
+    <sheet name="Bandhan Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="PNB Housing Finance" sheetId="25" r:id="rId25"/>
+    <sheet name="KTDFC" sheetId="26" r:id="rId26"/>
+    <sheet name="LIC Housing Finance" sheetId="27" r:id="rId27"/>
   </sheets>
 </workbook>
 </file>
@@ -583,132 +582,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 45 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 to 184 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
-      </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
-      </c>
-      <c r="B6">
-        <v>6.25</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
-      </c>
-      <c r="B7">
-        <v>6.3</v>
-      </c>
-      <c r="C7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
-      </c>
-      <c r="B8">
-        <v>6.45</v>
-      </c>
-      <c r="C8">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -729,73 +602,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 - 14 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>15 - 30 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>31 - 45 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>46 - 90 Days</v>
       </c>
       <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>91 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>92 Days - 179 Days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>180 Days</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -806,18 +679,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>181 Days to 269 Days</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>270 Days</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -828,101 +701,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>271 Days to 363 Days</v>
       </c>
       <c r="B11">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>364 Days</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>365 Days to less than 15 Months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>15 Months - less than 18 Months</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>18 months - less than 2 years</v>
       </c>
       <c r="B15">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="C15">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>2 years- less than 3 years</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>3 years and above but less than 4 years</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>4 years and above but less than 5 years</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years to 10 years</v>
+        <v>5 years and above upto and inclusive of 10 years</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -932,232 +805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1426,7 +1074,210 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C17"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 days to 179 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 days</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B9">
+        <v>5.75</v>
+      </c>
+      <c r="C9">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>270 days to 364 days</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 Year to below 1 Year 6 Month</v>
+      </c>
+      <c r="B12">
+        <v>6.75</v>
+      </c>
+      <c r="C12">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 Year 6 months to below 1 Year 7 months</v>
+      </c>
+      <c r="B13">
+        <v>6.9</v>
+      </c>
+      <c r="C13">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>1 Year 7 months to below 2 Years</v>
+      </c>
+      <c r="B14">
+        <v>6.9</v>
+      </c>
+      <c r="C14">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2 Years to 3 Years</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Above 3 Years up to below 61 Months</v>
+      </c>
+      <c r="B16">
+        <v>6.65</v>
+      </c>
+      <c r="C16">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>61 Months and above</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1607,7 +1458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1744,7 +1595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1926,7 +1777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2081,6 +1932,198 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2110,164 +2153,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
         <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -2279,7 +2322,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2299,43 +2342,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2343,128 +2386,95 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2705,24 +2715,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -2730,109 +2740,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -2843,6 +2853,413 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2864,7 +3281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -2875,535 +3292,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3430,134 +3440,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3568,165 +3578,6 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -3830,7 +3681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3912,7 +3763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
@@ -4462,203 +4313,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months</v>
-      </c>
-      <c r="B2">
-        <v>6.6</v>
-      </c>
-      <c r="C2">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B3">
-        <v>6.6</v>
-      </c>
-      <c r="C3">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>24 months</v>
-      </c>
-      <c r="B4">
-        <v>6.85</v>
-      </c>
-      <c r="C4">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B5">
-        <v>6.85</v>
-      </c>
-      <c r="C5">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>36 months</v>
-      </c>
-      <c r="B6">
-        <v>7.4</v>
-      </c>
-      <c r="C6">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>42 months</v>
-      </c>
-      <c r="B7">
-        <v>7.4</v>
-      </c>
-      <c r="C7">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>48 months</v>
-      </c>
-      <c r="B8">
-        <v>7.45</v>
-      </c>
-      <c r="C8">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>60 months</v>
-      </c>
-      <c r="B9">
-        <v>7.45</v>
-      </c>
-      <c r="C9">
-        <v>7.8</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months</v>
-      </c>
-      <c r="B2">
-        <v>6.85</v>
-      </c>
-      <c r="C2">
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months (digital only)</v>
-      </c>
-      <c r="B3">
-        <v>7.1</v>
-      </c>
-      <c r="C3">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months – 23 months</v>
-      </c>
-      <c r="B4">
-        <v>7.05</v>
-      </c>
-      <c r="C4">
-        <v>7.55</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>24 months – 35 months</v>
-      </c>
-      <c r="B5">
-        <v>7.1</v>
-      </c>
-      <c r="C5">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>36 months – 60 months</v>
-      </c>
-      <c r="B6">
-        <v>7.5</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -4893,7 +4547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -5028,4 +4682,355 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 45 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 to 184 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>185 to &lt; 1 Year</v>
+      </c>
+      <c r="B5">
+        <v>5.5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1 Year to &lt; 18 Months</v>
+      </c>
+      <c r="B6">
+        <v>6.25</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>18 Months to 2 Years</v>
+      </c>
+      <c r="B7">
+        <v>6.3</v>
+      </c>
+      <c r="C7">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2 Years 1 Day to 3 Years</v>
+      </c>
+      <c r="B8">
+        <v>6.45</v>
+      </c>
+      <c r="C8">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>3 Years 1 Day to 5 Years</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>5 Years 1 Day to 10 Years</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 – 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 – 29 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 – 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.25</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 – 60 days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>61 days - 87 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>88 days – 3 months 24 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>3 months 25 days &lt; 4 months</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>4 months &lt; 6 months</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>6 months &lt; 9 months</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
+        <v>6.5</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -8,28 +8,30 @@
     <sheet name="Utkarsh Small Finance Bank" sheetId="3" r:id="rId3"/>
     <sheet name="Unity Small Finance Bank" sheetId="4" r:id="rId4"/>
     <sheet name="Bajaj Finance" sheetId="5" r:id="rId5"/>
-    <sheet name="HDFC Bank" sheetId="6" r:id="rId6"/>
-    <sheet name="SBI" sheetId="7" r:id="rId7"/>
-    <sheet name="ICICI Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="Axis Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="PNB" sheetId="11" r:id="rId11"/>
-    <sheet name="IndusInd Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="Yes Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="IDFC First Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Indian Overseas Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Canara Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Bank of Baroda" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of India" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of Maharashtra" sheetId="19" r:id="rId19"/>
-    <sheet name="RBL Bank" sheetId="20" r:id="rId20"/>
-    <sheet name="IDBI Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="Indian Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Central Bank of India" sheetId="23" r:id="rId23"/>
-    <sheet name="Bandhan Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="PNB Housing Finance" sheetId="25" r:id="rId25"/>
-    <sheet name="KTDFC" sheetId="26" r:id="rId26"/>
-    <sheet name="LIC Housing Finance" sheetId="27" r:id="rId27"/>
+    <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
+    <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
+    <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="SBI" sheetId="9" r:id="rId9"/>
+    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="PNB" sheetId="13" r:id="rId13"/>
+    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
+    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
+    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
+    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
+    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
+    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
   </sheets>
 </workbook>
 </file>
@@ -582,6 +584,132 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 45 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 to 184 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>185 to &lt; 1 Year</v>
+      </c>
+      <c r="B5">
+        <v>5.5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1 Year to &lt; 18 Months</v>
+      </c>
+      <c r="B6">
+        <v>6.25</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>18 Months to 2 Years</v>
+      </c>
+      <c r="B7">
+        <v>6.3</v>
+      </c>
+      <c r="C7">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2 Years 1 Day to 3 Years</v>
+      </c>
+      <c r="B8">
+        <v>6.45</v>
+      </c>
+      <c r="C8">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>3 Years 1 Day to 5 Years</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>5 Years 1 Day to 10 Years</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -602,73 +730,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 - 30 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 - 90 Days</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 Days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 Days</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -679,18 +807,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
         <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -701,101 +829,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>364 Days</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -805,7 +933,232 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1074,7 +1427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1273,324 +1626,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 120 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>121 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 271 days</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>12 months</v>
-      </c>
-      <c r="B9">
-        <v>6.65</v>
-      </c>
-      <c r="C9">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
-      </c>
-      <c r="B10">
-        <v>6.75</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.75</v>
-      </c>
-      <c r="C11">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
-      </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
-      </c>
-      <c r="B14">
-        <v>7</v>
-      </c>
-      <c r="C14">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B15">
-        <v>6.75</v>
-      </c>
-      <c r="C15">
-        <v>7.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days – 29 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>30 days – 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days – 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days – 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days – less than 1 Year</v>
-      </c>
-      <c r="B6">
-        <v>6.5</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>1 year – 370 days</v>
-      </c>
-      <c r="B7">
-        <v>6.5</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>371 days – 499 days</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>500 days – 3 years</v>
-      </c>
-      <c r="B9">
-        <v>7.25</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>3 years 1 day – 5 years</v>
-      </c>
-      <c r="B10">
-        <v>6.75</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>5 years 1 day – 10 years</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1617,18 +1652,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7-14 Days*</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-29 Days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
         <v>3.5</v>
@@ -1639,135 +1674,134 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30-45 Days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46-60 Days</v>
+        <v>91 days to 120 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61-90 Days</v>
+        <v>121 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91-120 Days</v>
+        <v>181 days to 271 days</v>
       </c>
       <c r="B7">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>121-179 Days</v>
+        <v>272 days to less than 12 months</v>
       </c>
       <c r="B8">
-        <v>2.9</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>3.4</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>180-269 Days</v>
+        <v>12 months</v>
       </c>
       <c r="B9">
-        <v>4.75</v>
+        <v>6.65</v>
       </c>
       <c r="C9">
-        <v>5.25</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days to &lt; 1 Year</v>
+        <v>12 months 1 day to less than 18 months</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1 Year</v>
+        <v>18 months</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
-(Except 444 Days)</v>
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months 1 day to less than 24 months</v>
       </c>
       <c r="B12">
-        <v>6.4</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.9</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>444 Days</v>
+        <v>24 months to less than 36 months</v>
       </c>
       <c r="B13">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2 Years to &lt; 3 Years</v>
+        <v>36 months to less than 60 months</v>
       </c>
       <c r="B14">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>6.9</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3 Years and above</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B15">
-        <v>6.1</v>
+        <v>6.75</v>
       </c>
       <c r="C15">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1778,6 +1812,325 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C11"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days – 29 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>30 days – 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days – 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days – 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days – less than 1 Year</v>
+      </c>
+      <c r="B6">
+        <v>6.5</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1 year – 370 days</v>
+      </c>
+      <c r="B7">
+        <v>6.5</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>371 days – 499 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>500 days – 3 years</v>
+      </c>
+      <c r="B9">
+        <v>7.25</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>3 years 1 day – 5 years</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>5 years 1 day – 10 years</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7-14 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15-29 Days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30-45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3.5</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46-60 Days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>61-90 Days</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>91-120 Days</v>
+      </c>
+      <c r="B7">
+        <v>3.5</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>121-179 Days</v>
+      </c>
+      <c r="B8">
+        <v>2.9</v>
+      </c>
+      <c r="C8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>180-269 Days</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days to &lt; 1 Year</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt; 1 Year to &lt; 2 Years
+(Except 444 Days)</v>
+      </c>
+      <c r="B12">
+        <v>6.4</v>
+      </c>
+      <c r="C12">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>444 Days</v>
+      </c>
+      <c r="B13">
+        <v>6.6</v>
+      </c>
+      <c r="C13">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 Years to &lt; 3 Years</v>
+      </c>
+      <c r="B14">
+        <v>6.4</v>
+      </c>
+      <c r="C14">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 Years and above</v>
+      </c>
+      <c r="B15">
+        <v>6.1</v>
+      </c>
+      <c r="C15">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1936,7 +2289,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -2124,357 +2477,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 30 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 179 days</v>
-      </c>
-      <c r="B6">
-        <v>4.25</v>
-      </c>
-      <c r="C6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>180 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.3</v>
-      </c>
-      <c r="C11">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>450 days</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.6</v>
-      </c>
-      <c r="C2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 119 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>120 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to 364 days</v>
-      </c>
-      <c r="B8">
-        <v>5.25</v>
-      </c>
-      <c r="C8">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
-      </c>
-      <c r="B10">
-        <v>6.15</v>
-      </c>
-      <c r="C10">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
-      </c>
-      <c r="B11">
-        <v>5.25</v>
-      </c>
-      <c r="C11">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 5 years</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2695,6 +2697,198 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2715,24 +2909,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2740,109 +2934,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -2852,7 +3046,166 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -3067,7 +3420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -3259,7 +3612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3418,7 +3771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3577,7 +3930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -3681,7 +4034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3763,7 +4116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
@@ -4313,6 +4666,203 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C9"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B2">
+        <v>6.6</v>
+      </c>
+      <c r="C2">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B3">
+        <v>6.6</v>
+      </c>
+      <c r="C3">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>24 months</v>
+      </c>
+      <c r="B4">
+        <v>6.85</v>
+      </c>
+      <c r="C4">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B5">
+        <v>6.85</v>
+      </c>
+      <c r="C5">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>36 months</v>
+      </c>
+      <c r="B6">
+        <v>7.4</v>
+      </c>
+      <c r="C6">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>42 months</v>
+      </c>
+      <c r="B7">
+        <v>7.4</v>
+      </c>
+      <c r="C7">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>48 months</v>
+      </c>
+      <c r="B8">
+        <v>7.45</v>
+      </c>
+      <c r="C8">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>60 months</v>
+      </c>
+      <c r="B9">
+        <v>7.45</v>
+      </c>
+      <c r="C9">
+        <v>7.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B2">
+        <v>6.85</v>
+      </c>
+      <c r="C2">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months (digital only)</v>
+      </c>
+      <c r="B3">
+        <v>7.1</v>
+      </c>
+      <c r="C3">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months – 23 months</v>
+      </c>
+      <c r="B4">
+        <v>7.05</v>
+      </c>
+      <c r="C4">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>24 months – 35 months</v>
+      </c>
+      <c r="B5">
+        <v>7.1</v>
+      </c>
+      <c r="C5">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>36 months – 60 months</v>
+      </c>
+      <c r="B6">
+        <v>7.5</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -4547,7 +5097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -4682,355 +5232,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 45 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 to 184 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
-      </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
-      </c>
-      <c r="B6">
-        <v>6.25</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
-      </c>
-      <c r="B7">
-        <v>6.3</v>
-      </c>
-      <c r="C7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
-      </c>
-      <c r="B8">
-        <v>6.45</v>
-      </c>
-      <c r="C8">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 – 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 – 29 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 – 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.25</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 – 60 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61 days - 87 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
-      </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -20,18 +20,19 @@
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
-    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
-    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
-    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
-    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
-    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
+    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
+    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
+    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
+    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
+    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
+    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
   </sheets>
 </workbook>
 </file>
@@ -2132,6 +2133,187 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 29 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>30 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.25</v>
+      </c>
+      <c r="C3">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>182 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to less than 15 Months</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>15 Months</v>
+      </c>
+      <c r="B11">
+        <v>6.65</v>
+      </c>
+      <c r="C11">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 15 Months to 24 Months</v>
+      </c>
+      <c r="B12">
+        <v>6.4</v>
+      </c>
+      <c r="C12">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 24 months to less than 48 months</v>
+      </c>
+      <c r="B13">
+        <v>6.5</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>48 months</v>
+      </c>
+      <c r="B14">
+        <v>6.7</v>
+      </c>
+      <c r="C14">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 48 months to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>6.4</v>
+      </c>
+      <c r="C15">
+        <v>6.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2285,198 +2467,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2720,164 +2710,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>181 days to 210 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>211 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days &amp; above and less than 1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 400 days</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 400 days and upto 2 Years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above 2 Years and upto 3 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 3 Years and upto 5 Years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>Above 5 Years and upto 10 Years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>Above 10 years (MACAD only)</v>
       </c>
       <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
         <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="C16">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -2889,7 +2879,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2909,43 +2899,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2953,95 +2943,128 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3068,24 +3091,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -3093,109 +3116,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -3206,6 +3229,165 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -3420,7 +3602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -3608,165 +3790,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3793,134 +3816,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3931,6 +3954,165 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
   <cols>
@@ -4034,7 +4216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -4112,99 +4294,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B4">
-        <v>6.75</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
-      </c>
-      <c r="C5">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B6">
-        <v>6.85</v>
-      </c>
-      <c r="C6">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B7">
-        <v>6.9</v>
-      </c>
-      <c r="C7">
-        <v>7.15</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4353,6 +4442,99 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C7"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B4">
+        <v>6.75</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B5">
+        <v>6.8</v>
+      </c>
+      <c r="C5">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B6">
+        <v>6.85</v>
+      </c>
+      <c r="C6">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B7">
+        <v>6.9</v>
+      </c>
+      <c r="C7">
+        <v>7.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -20,19 +20,18 @@
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Indian Overseas Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Federal Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Canara Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Baroda" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of India" sheetId="21" r:id="rId21"/>
-    <sheet name="Bank of Maharashtra" sheetId="22" r:id="rId22"/>
-    <sheet name="RBL Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="IDBI Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Indian Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="Central Bank of India" sheetId="26" r:id="rId26"/>
-    <sheet name="Bandhan Bank" sheetId="27" r:id="rId27"/>
-    <sheet name="PNB Housing Finance" sheetId="28" r:id="rId28"/>
-    <sheet name="KTDFC" sheetId="29" r:id="rId29"/>
-    <sheet name="LIC Housing Finance" sheetId="30" r:id="rId30"/>
+    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
+    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
+    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
+    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
+    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
+    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
   </sheets>
 </workbook>
 </file>
@@ -2133,187 +2132,6 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 29 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>30 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.25</v>
-      </c>
-      <c r="C3">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.25</v>
-      </c>
-      <c r="C4">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>182 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to less than 15 Months</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>15 Months</v>
-      </c>
-      <c r="B11">
-        <v>6.65</v>
-      </c>
-      <c r="C11">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 15 Months to 24 Months</v>
-      </c>
-      <c r="B12">
-        <v>6.4</v>
-      </c>
-      <c r="C12">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 24 months to less than 48 months</v>
-      </c>
-      <c r="B13">
-        <v>6.5</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>48 months</v>
-      </c>
-      <c r="B14">
-        <v>6.7</v>
-      </c>
-      <c r="C14">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 48 months to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>6.4</v>
-      </c>
-      <c r="C15">
-        <v>6.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2467,6 +2285,198 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2710,164 +2720,164 @@
         <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
         <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
+        <v>5 years to less than 8 years</v>
       </c>
       <c r="B15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+        <v>8 years and above to 10 years</v>
       </c>
       <c r="B16">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -2879,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2899,43 +2909,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2943,128 +2953,95 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3091,24 +3068,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -3116,109 +3093,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3229,6 +3206,413 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3250,7 +3634,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3261,535 +3645,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width=